--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118762626</v>
+        <v>118769846</v>
       </c>
       <c r="B27" t="n">
-        <v>97846</v>
+        <v>79594</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3247,41 +3247,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474988</v>
+        <v>474860</v>
       </c>
       <c r="R27" t="n">
-        <v>6852930</v>
+        <v>6852995</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3325,19 +3325,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118766096</v>
+        <v>118762626</v>
       </c>
       <c r="B28" t="n">
         <v>97846</v>
@@ -3377,13 +3377,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>475291</v>
+        <v>474988</v>
       </c>
       <c r="R28" t="n">
-        <v>6853381</v>
+        <v>6852930</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118769846</v>
+        <v>118766096</v>
       </c>
       <c r="B29" t="n">
-        <v>79594</v>
+        <v>97846</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3451,41 +3451,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474860</v>
+        <v>475291</v>
       </c>
       <c r="R29" t="n">
-        <v>6852995</v>
+        <v>6853381</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3529,12 +3529,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118762480</v>
+        <v>118769874</v>
       </c>
       <c r="B36" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4165,41 +4165,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474949</v>
+        <v>475265</v>
       </c>
       <c r="R36" t="n">
-        <v>6852843</v>
+        <v>6853105</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4243,22 +4243,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118769874</v>
+        <v>118766285</v>
       </c>
       <c r="B37" t="n">
-        <v>78484</v>
+        <v>79566</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4271,37 +4271,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475265</v>
+        <v>475155</v>
       </c>
       <c r="R37" t="n">
-        <v>6853105</v>
+        <v>6853357</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4357,10 +4357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118766285</v>
+        <v>118762480</v>
       </c>
       <c r="B38" t="n">
-        <v>79566</v>
+        <v>97846</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4369,38 +4369,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475155</v>
+        <v>474949</v>
       </c>
       <c r="R38" t="n">
-        <v>6853357</v>
+        <v>6852843</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4447,12 +4447,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5714,7 +5714,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118769869</v>
+        <v>118769865</v>
       </c>
       <c r="B51" t="n">
         <v>97846</v>
@@ -5754,10 +5754,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474841</v>
+        <v>475295</v>
       </c>
       <c r="R51" t="n">
-        <v>6852986</v>
+        <v>6853180</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5816,7 +5816,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118769865</v>
+        <v>118769869</v>
       </c>
       <c r="B52" t="n">
         <v>97846</v>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475295</v>
+        <v>474841</v>
       </c>
       <c r="R52" t="n">
-        <v>6853180</v>
+        <v>6852986</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -4459,10 +4459,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118765546</v>
+        <v>118762755</v>
       </c>
       <c r="B39" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4471,41 +4471,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475240</v>
+        <v>475026</v>
       </c>
       <c r="R39" t="n">
-        <v>6853164</v>
+        <v>6852933</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4561,10 +4570,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118766686</v>
+        <v>118765546</v>
       </c>
       <c r="B40" t="n">
-        <v>79594</v>
+        <v>79565</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4573,41 +4582,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475054</v>
+        <v>475240</v>
       </c>
       <c r="R40" t="n">
-        <v>6853272</v>
+        <v>6853164</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4651,22 +4660,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118769848</v>
+        <v>118766686</v>
       </c>
       <c r="B41" t="n">
-        <v>79566</v>
+        <v>79594</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4675,41 +4684,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475286</v>
+        <v>475054</v>
       </c>
       <c r="R41" t="n">
-        <v>6853351</v>
+        <v>6853272</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4765,10 +4774,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118762755</v>
+        <v>118769848</v>
       </c>
       <c r="B42" t="n">
-        <v>97846</v>
+        <v>79566</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4777,50 +4786,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475026</v>
+        <v>475286</v>
       </c>
       <c r="R42" t="n">
-        <v>6852933</v>
+        <v>6853351</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4864,12 +4864,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118763114</v>
+        <v>118762886</v>
       </c>
       <c r="B2" t="n">
         <v>79565</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474930</v>
+        <v>474862</v>
       </c>
       <c r="R2" t="n">
-        <v>6853098</v>
+        <v>6852981</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118769855</v>
+        <v>118769865</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475284</v>
+        <v>475295</v>
       </c>
       <c r="R3" t="n">
-        <v>6853186</v>
+        <v>6853180</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118769844</v>
+        <v>118765546</v>
       </c>
       <c r="B4" t="n">
-        <v>90469</v>
+        <v>79565</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474897</v>
+        <v>475240</v>
       </c>
       <c r="R4" t="n">
-        <v>6852835</v>
+        <v>6853164</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118766233</v>
+        <v>118769844</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475181</v>
+        <v>474897</v>
       </c>
       <c r="R5" t="n">
-        <v>6853364</v>
+        <v>6852835</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118766297</v>
+        <v>118769861</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475153</v>
+        <v>475079</v>
       </c>
       <c r="R6" t="n">
-        <v>6853357</v>
+        <v>6853115</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1159,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118766206</v>
+        <v>118764888</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1221,17 +1226,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475201</v>
+        <v>475321</v>
       </c>
       <c r="R7" t="n">
-        <v>6853392</v>
+        <v>6853346</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,22 +1280,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118766005</v>
+        <v>118769852</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,41 +1304,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475286</v>
+        <v>475281</v>
       </c>
       <c r="R8" t="n">
-        <v>6853383</v>
+        <v>6853211</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118769860</v>
+        <v>118763114</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,41 +1406,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475001</v>
+        <v>474930</v>
       </c>
       <c r="R9" t="n">
-        <v>6852915</v>
+        <v>6853098</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1470,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,22 +1484,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118769863</v>
+        <v>118769873</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>56272</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>208260</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475302</v>
+        <v>474840</v>
       </c>
       <c r="R10" t="n">
-        <v>6853363</v>
+        <v>6852984</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1603,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118766370</v>
+        <v>118762626</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1643,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475119</v>
+        <v>474988</v>
       </c>
       <c r="R11" t="n">
-        <v>6853325</v>
+        <v>6852930</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118769873</v>
+        <v>118766394</v>
       </c>
       <c r="B12" t="n">
-        <v>56272</v>
+        <v>97846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,41 +1712,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208260</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474840</v>
+        <v>475130</v>
       </c>
       <c r="R12" t="n">
-        <v>6852984</v>
+        <v>6853328</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1807,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118769859</v>
+        <v>118765116</v>
       </c>
       <c r="B13" t="n">
-        <v>97750</v>
+        <v>97846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,41 +1814,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475091</v>
+        <v>475300</v>
       </c>
       <c r="R13" t="n">
-        <v>6853271</v>
+        <v>6853368</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1909,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118764109</v>
+        <v>118766686</v>
       </c>
       <c r="B14" t="n">
-        <v>78129</v>
+        <v>79594</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,41 +1916,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475259</v>
+        <v>475054</v>
       </c>
       <c r="R14" t="n">
-        <v>6853227</v>
+        <v>6853272</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1999,22 +1994,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118766394</v>
+        <v>118766297</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2023,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475130</v>
+        <v>475153</v>
       </c>
       <c r="R15" t="n">
-        <v>6853328</v>
+        <v>6853357</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118769867</v>
+        <v>118769870</v>
       </c>
       <c r="B16" t="n">
         <v>97846</v>
@@ -2153,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475281</v>
+        <v>474936</v>
       </c>
       <c r="R16" t="n">
-        <v>6853098</v>
+        <v>6852846</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2215,7 +2210,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118765071</v>
+        <v>118766078</v>
       </c>
       <c r="B17" t="n">
         <v>97846</v>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475339</v>
+        <v>475291</v>
       </c>
       <c r="R17" t="n">
-        <v>6853351</v>
+        <v>6853381</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2291,6 +2286,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>15-tal individer</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118766193</v>
+        <v>118765092</v>
       </c>
       <c r="B18" t="n">
         <v>97846</v>
@@ -2357,13 +2357,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475229</v>
+        <v>475341</v>
       </c>
       <c r="R18" t="n">
-        <v>6853392</v>
+        <v>6853346</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118766023</v>
+        <v>118769860</v>
       </c>
       <c r="B19" t="n">
         <v>97846</v>
@@ -2455,14 +2455,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475261</v>
+        <v>475001</v>
       </c>
       <c r="R19" t="n">
-        <v>6853378</v>
+        <v>6852915</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2495,6 +2495,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2521,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118769847</v>
+        <v>118769863</v>
       </c>
       <c r="B20" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2533,25 +2538,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474904</v>
+        <v>475302</v>
       </c>
       <c r="R20" t="n">
-        <v>6852836</v>
+        <v>6853363</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2623,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118765086</v>
+        <v>118769847</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2635,41 +2640,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475303</v>
+        <v>474904</v>
       </c>
       <c r="R21" t="n">
-        <v>6853364</v>
+        <v>6852836</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2725,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118765116</v>
+        <v>118766233</v>
       </c>
       <c r="B22" t="n">
         <v>97846</v>
@@ -2765,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475300</v>
+        <v>475181</v>
       </c>
       <c r="R22" t="n">
-        <v>6853368</v>
+        <v>6853364</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2827,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118769856</v>
+        <v>118762153</v>
       </c>
       <c r="B23" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2839,41 +2844,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475300</v>
+        <v>474905</v>
       </c>
       <c r="R23" t="n">
-        <v>6853182</v>
+        <v>6852851</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2917,22 +2922,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118769852</v>
+        <v>118769866</v>
       </c>
       <c r="B24" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2941,25 +2946,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475281</v>
+        <v>475289</v>
       </c>
       <c r="R24" t="n">
-        <v>6853211</v>
+        <v>6853167</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3031,7 +3036,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118765092</v>
+        <v>118766126</v>
       </c>
       <c r="B25" t="n">
         <v>97846</v>
@@ -3067,17 +3072,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475341</v>
+        <v>475221</v>
       </c>
       <c r="R25" t="n">
-        <v>6853346</v>
+        <v>6853376</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3121,19 +3126,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118763353</v>
+        <v>118769867</v>
       </c>
       <c r="B26" t="n">
         <v>97846</v>
@@ -3169,17 +3174,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475052</v>
+        <v>475281</v>
       </c>
       <c r="R26" t="n">
-        <v>6853129</v>
+        <v>6853098</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3223,22 +3228,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118769846</v>
+        <v>118762495</v>
       </c>
       <c r="B27" t="n">
-        <v>79594</v>
+        <v>97846</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3247,41 +3252,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474860</v>
+        <v>474949</v>
       </c>
       <c r="R27" t="n">
-        <v>6852995</v>
+        <v>6852843</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3325,19 +3330,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118762626</v>
+        <v>118766193</v>
       </c>
       <c r="B28" t="n">
         <v>97846</v>
@@ -3377,13 +3382,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474988</v>
+        <v>475229</v>
       </c>
       <c r="R28" t="n">
-        <v>6852930</v>
+        <v>6853392</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3439,10 +3444,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118766096</v>
+        <v>118766652</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>79566</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3451,41 +3456,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475291</v>
+        <v>475065</v>
       </c>
       <c r="R29" t="n">
-        <v>6853381</v>
+        <v>6853275</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3529,19 +3534,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118762886</v>
+        <v>118769855</v>
       </c>
       <c r="B30" t="n">
         <v>79565</v>
@@ -3577,17 +3582,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474862</v>
+        <v>475284</v>
       </c>
       <c r="R30" t="n">
-        <v>6852981</v>
+        <v>6853186</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3631,19 +3636,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118765456</v>
+        <v>118769856</v>
       </c>
       <c r="B31" t="n">
         <v>79565</v>
@@ -3679,17 +3684,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475349</v>
+        <v>475300</v>
       </c>
       <c r="R31" t="n">
-        <v>6853384</v>
+        <v>6853182</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3745,7 +3750,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118766126</v>
+        <v>118766206</v>
       </c>
       <c r="B32" t="n">
         <v>97846</v>
@@ -3785,10 +3790,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475221</v>
+        <v>475201</v>
       </c>
       <c r="R32" t="n">
-        <v>6853376</v>
+        <v>6853392</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3821,6 +3826,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3847,7 +3857,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118762153</v>
+        <v>118766302</v>
       </c>
       <c r="B33" t="n">
         <v>97846</v>
@@ -3880,20 +3890,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474905</v>
+        <v>475179</v>
       </c>
       <c r="R33" t="n">
-        <v>6852851</v>
+        <v>6853360</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3949,10 +3968,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118769870</v>
+        <v>118764109</v>
       </c>
       <c r="B34" t="n">
-        <v>97846</v>
+        <v>78129</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3961,41 +3980,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474936</v>
+        <v>475259</v>
       </c>
       <c r="R34" t="n">
-        <v>6852846</v>
+        <v>6853227</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4039,22 +4058,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118764888</v>
+        <v>118769846</v>
       </c>
       <c r="B35" t="n">
-        <v>97846</v>
+        <v>79594</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4063,41 +4082,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475321</v>
+        <v>474860</v>
       </c>
       <c r="R35" t="n">
-        <v>6853346</v>
+        <v>6852995</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4141,22 +4160,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118769874</v>
+        <v>118770271</v>
       </c>
       <c r="B36" t="n">
-        <v>78484</v>
+        <v>57443</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4169,34 +4188,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475265</v>
+        <v>475175</v>
       </c>
       <c r="R36" t="n">
-        <v>6853105</v>
+        <v>6853143</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4255,10 +4282,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118766285</v>
+        <v>118766370</v>
       </c>
       <c r="B37" t="n">
-        <v>79566</v>
+        <v>97846</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4267,41 +4294,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475155</v>
+        <v>475119</v>
       </c>
       <c r="R37" t="n">
-        <v>6853357</v>
+        <v>6853325</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4345,19 +4372,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118762480</v>
+        <v>118769862</v>
       </c>
       <c r="B38" t="n">
         <v>97846</v>
@@ -4393,17 +4420,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474949</v>
+        <v>475095</v>
       </c>
       <c r="R38" t="n">
-        <v>6852843</v>
+        <v>6853273</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4447,19 +4474,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118762755</v>
+        <v>118769869</v>
       </c>
       <c r="B39" t="n">
         <v>97846</v>
@@ -4492,29 +4519,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475026</v>
+        <v>474841</v>
       </c>
       <c r="R39" t="n">
-        <v>6852933</v>
+        <v>6852986</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4558,22 +4576,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118765546</v>
+        <v>118766023</v>
       </c>
       <c r="B40" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4582,38 +4600,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475240</v>
+        <v>475261</v>
       </c>
       <c r="R40" t="n">
-        <v>6853164</v>
+        <v>6853378</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4660,22 +4678,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118766686</v>
+        <v>118769853</v>
       </c>
       <c r="B41" t="n">
-        <v>79594</v>
+        <v>79565</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4684,41 +4702,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475054</v>
+        <v>475286</v>
       </c>
       <c r="R41" t="n">
-        <v>6853272</v>
+        <v>6853198</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4774,10 +4792,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118769848</v>
+        <v>118769859</v>
       </c>
       <c r="B42" t="n">
-        <v>79566</v>
+        <v>97750</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4786,25 +4804,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>220093</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4814,10 +4832,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475286</v>
+        <v>475091</v>
       </c>
       <c r="R42" t="n">
-        <v>6853351</v>
+        <v>6853271</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4876,10 +4894,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118766652</v>
+        <v>118763353</v>
       </c>
       <c r="B43" t="n">
-        <v>79566</v>
+        <v>97846</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4888,41 +4906,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475065</v>
+        <v>475052</v>
       </c>
       <c r="R43" t="n">
-        <v>6853275</v>
+        <v>6853129</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4966,19 +4984,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118769853</v>
+        <v>118765456</v>
       </c>
       <c r="B44" t="n">
         <v>79565</v>
@@ -5014,17 +5032,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475286</v>
+        <v>475349</v>
       </c>
       <c r="R44" t="n">
-        <v>6853198</v>
+        <v>6853384</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5080,7 +5098,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118766412</v>
+        <v>118762755</v>
       </c>
       <c r="B45" t="n">
         <v>97846</v>
@@ -5113,20 +5131,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475111</v>
+        <v>475026</v>
       </c>
       <c r="R45" t="n">
-        <v>6853306</v>
+        <v>6852933</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5170,19 +5197,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118766302</v>
+        <v>118766005</v>
       </c>
       <c r="B46" t="n">
         <v>97846</v>
@@ -5215,29 +5242,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475179</v>
+        <v>475286</v>
       </c>
       <c r="R46" t="n">
-        <v>6853360</v>
+        <v>6853383</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5281,22 +5299,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118769862</v>
+        <v>118769848</v>
       </c>
       <c r="B47" t="n">
-        <v>97846</v>
+        <v>79566</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5305,25 +5323,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5333,10 +5351,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475095</v>
+        <v>475286</v>
       </c>
       <c r="R47" t="n">
-        <v>6853273</v>
+        <v>6853351</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5395,10 +5413,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118770271</v>
+        <v>118766285</v>
       </c>
       <c r="B48" t="n">
-        <v>57443</v>
+        <v>79566</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5411,45 +5429,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475175</v>
+        <v>475155</v>
       </c>
       <c r="R48" t="n">
-        <v>6853143</v>
+        <v>6853357</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5505,7 +5515,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118769861</v>
+        <v>118765071</v>
       </c>
       <c r="B49" t="n">
         <v>97846</v>
@@ -5541,17 +5551,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475079</v>
+        <v>475339</v>
       </c>
       <c r="R49" t="n">
-        <v>6853115</v>
+        <v>6853351</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5581,11 +5591,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5600,19 +5605,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118769866</v>
+        <v>118766412</v>
       </c>
       <c r="B50" t="n">
         <v>97846</v>
@@ -5648,17 +5653,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475289</v>
+        <v>475111</v>
       </c>
       <c r="R50" t="n">
-        <v>6853167</v>
+        <v>6853306</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5714,7 +5719,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118769865</v>
+        <v>118765086</v>
       </c>
       <c r="B51" t="n">
         <v>97846</v>
@@ -5750,17 +5755,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475295</v>
+        <v>475303</v>
       </c>
       <c r="R51" t="n">
-        <v>6853180</v>
+        <v>6853364</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5816,10 +5821,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118769869</v>
+        <v>118769874</v>
       </c>
       <c r="B52" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5828,25 +5833,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5856,10 +5861,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474841</v>
+        <v>475265</v>
       </c>
       <c r="R52" t="n">
-        <v>6852986</v>
+        <v>6853105</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118769873</v>
+        <v>118766686</v>
       </c>
       <c r="B10" t="n">
-        <v>56272</v>
+        <v>79594</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,37 +1512,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208260</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474840</v>
+        <v>475054</v>
       </c>
       <c r="R10" t="n">
-        <v>6852984</v>
+        <v>6853272</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118766686</v>
+        <v>118769873</v>
       </c>
       <c r="B14" t="n">
-        <v>79594</v>
+        <v>56272</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,37 +1920,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>208260</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475054</v>
+        <v>474840</v>
       </c>
       <c r="R14" t="n">
-        <v>6853272</v>
+        <v>6852984</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3750,10 +3750,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118766206</v>
+        <v>118764109</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>78129</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3762,41 +3762,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475201</v>
+        <v>475259</v>
       </c>
       <c r="R32" t="n">
-        <v>6853392</v>
+        <v>6853227</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3826,11 +3826,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3845,19 +3840,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118766302</v>
+        <v>118766206</v>
       </c>
       <c r="B33" t="n">
         <v>97846</v>
@@ -3890,29 +3885,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>475179</v>
+        <v>475201</v>
       </c>
       <c r="R33" t="n">
-        <v>6853360</v>
+        <v>6853392</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3942,6 +3928,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3956,22 +3947,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118764109</v>
+        <v>118766302</v>
       </c>
       <c r="B34" t="n">
-        <v>78129</v>
+        <v>97846</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3980,38 +3971,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475259</v>
+        <v>475179</v>
       </c>
       <c r="R34" t="n">
-        <v>6853227</v>
+        <v>6853360</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118769846</v>
+        <v>118766370</v>
       </c>
       <c r="B35" t="n">
-        <v>79594</v>
+        <v>97846</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4082,41 +4082,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474860</v>
+        <v>475119</v>
       </c>
       <c r="R35" t="n">
-        <v>6852995</v>
+        <v>6853325</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4160,22 +4160,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118770271</v>
+        <v>118769846</v>
       </c>
       <c r="B36" t="n">
-        <v>57443</v>
+        <v>79594</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4184,46 +4184,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475175</v>
+        <v>474860</v>
       </c>
       <c r="R36" t="n">
-        <v>6853143</v>
+        <v>6852995</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4282,10 +4274,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118766370</v>
+        <v>118770271</v>
       </c>
       <c r="B37" t="n">
-        <v>97846</v>
+        <v>57443</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4294,41 +4286,49 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475119</v>
+        <v>475175</v>
       </c>
       <c r="R37" t="n">
-        <v>6853325</v>
+        <v>6853143</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4372,12 +4372,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118769859</v>
+        <v>118763353</v>
       </c>
       <c r="B42" t="n">
-        <v>97750</v>
+        <v>97846</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4804,41 +4804,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475091</v>
+        <v>475052</v>
       </c>
       <c r="R42" t="n">
-        <v>6853271</v>
+        <v>6853129</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4882,22 +4882,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118763353</v>
+        <v>118769859</v>
       </c>
       <c r="B43" t="n">
-        <v>97846</v>
+        <v>97750</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4906,41 +4906,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475052</v>
+        <v>475091</v>
       </c>
       <c r="R43" t="n">
-        <v>6853129</v>
+        <v>6853271</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4984,12 +4984,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118769848</v>
+        <v>118765071</v>
       </c>
       <c r="B47" t="n">
-        <v>79566</v>
+        <v>97846</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5323,41 +5323,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475286</v>
+        <v>475339</v>
       </c>
       <c r="R47" t="n">
         <v>6853351</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5401,19 +5401,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118766285</v>
+        <v>118769848</v>
       </c>
       <c r="B48" t="n">
         <v>79566</v>
@@ -5449,17 +5449,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475155</v>
+        <v>475286</v>
       </c>
       <c r="R48" t="n">
-        <v>6853357</v>
+        <v>6853351</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5515,10 +5515,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118765071</v>
+        <v>118766285</v>
       </c>
       <c r="B49" t="n">
-        <v>97846</v>
+        <v>79566</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5527,41 +5527,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475339</v>
+        <v>475155</v>
       </c>
       <c r="R49" t="n">
-        <v>6853351</v>
+        <v>6853357</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5605,12 +5605,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118762886</v>
+        <v>118769873</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>56272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>208260</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474862</v>
+        <v>474840</v>
       </c>
       <c r="R2" t="n">
-        <v>6852981</v>
+        <v>6852984</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118769865</v>
+        <v>118763114</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475295</v>
+        <v>474930</v>
       </c>
       <c r="R3" t="n">
-        <v>6853180</v>
+        <v>6853098</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118765546</v>
+        <v>118769846</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
+        <v>79594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475240</v>
+        <v>474860</v>
       </c>
       <c r="R4" t="n">
-        <v>6853164</v>
+        <v>6852995</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118769844</v>
+        <v>118769860</v>
       </c>
       <c r="B5" t="n">
-        <v>90469</v>
+        <v>97846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474897</v>
+        <v>475001</v>
       </c>
       <c r="R5" t="n">
-        <v>6852835</v>
+        <v>6852915</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118769861</v>
+        <v>118765071</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1119,17 +1124,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475079</v>
+        <v>475339</v>
       </c>
       <c r="R6" t="n">
-        <v>6853115</v>
+        <v>6853351</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1159,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118764888</v>
+        <v>118765546</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475321</v>
+        <v>475240</v>
       </c>
       <c r="R7" t="n">
-        <v>6853346</v>
+        <v>6853164</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118769852</v>
+        <v>118764109</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
+        <v>78129</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,37 +1308,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475281</v>
+        <v>475259</v>
       </c>
       <c r="R8" t="n">
-        <v>6853211</v>
+        <v>6853227</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,22 +1382,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118763114</v>
+        <v>118763353</v>
       </c>
       <c r="B9" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,41 +1406,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474930</v>
+        <v>475052</v>
       </c>
       <c r="R9" t="n">
-        <v>6853098</v>
+        <v>6853129</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118766686</v>
+        <v>118764888</v>
       </c>
       <c r="B10" t="n">
-        <v>79594</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,41 +1508,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475054</v>
+        <v>475321</v>
       </c>
       <c r="R10" t="n">
-        <v>6853272</v>
+        <v>6853346</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1586,22 +1586,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118762626</v>
+        <v>118769856</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,41 +1610,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474988</v>
+        <v>475300</v>
       </c>
       <c r="R11" t="n">
-        <v>6852930</v>
+        <v>6853182</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1688,19 +1688,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118766394</v>
+        <v>118766126</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475130</v>
+        <v>475221</v>
       </c>
       <c r="R12" t="n">
-        <v>6853328</v>
+        <v>6853376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118765116</v>
+        <v>118769861</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -1838,17 +1838,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475300</v>
+        <v>475079</v>
       </c>
       <c r="R13" t="n">
-        <v>6853368</v>
+        <v>6853115</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1878,6 +1878,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118769873</v>
+        <v>118766394</v>
       </c>
       <c r="B14" t="n">
-        <v>56272</v>
+        <v>97846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,41 +1921,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208260</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474840</v>
+        <v>475130</v>
       </c>
       <c r="R14" t="n">
-        <v>6852984</v>
+        <v>6853328</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2006,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118766297</v>
+        <v>118762153</v>
       </c>
       <c r="B15" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,38 +2023,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475153</v>
+        <v>474905</v>
       </c>
       <c r="R15" t="n">
-        <v>6853357</v>
+        <v>6852851</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2096,22 +2101,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118769870</v>
+        <v>118769844</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2125,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474936</v>
+        <v>474897</v>
       </c>
       <c r="R16" t="n">
-        <v>6852846</v>
+        <v>6852835</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2210,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118766078</v>
+        <v>118769855</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,41 +2227,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475291</v>
+        <v>475284</v>
       </c>
       <c r="R17" t="n">
-        <v>6853381</v>
+        <v>6853186</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2286,11 +2291,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>15-tal individer</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2305,19 +2305,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118765092</v>
+        <v>118766193</v>
       </c>
       <c r="B18" t="n">
         <v>97846</v>
@@ -2357,13 +2357,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475341</v>
+        <v>475229</v>
       </c>
       <c r="R18" t="n">
-        <v>6853346</v>
+        <v>6853392</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118769860</v>
+        <v>118766652</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>79566</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,41 +2431,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475001</v>
+        <v>475065</v>
       </c>
       <c r="R19" t="n">
-        <v>6852915</v>
+        <v>6853275</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2495,11 +2495,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118769863</v>
+        <v>118766078</v>
       </c>
       <c r="B20" t="n">
         <v>97846</v>
@@ -2562,17 +2557,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475302</v>
+        <v>475291</v>
       </c>
       <c r="R20" t="n">
-        <v>6853363</v>
+        <v>6853381</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2602,6 +2597,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>15-tal individer</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2616,22 +2616,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118769847</v>
+        <v>118769863</v>
       </c>
       <c r="B21" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,25 +2640,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474904</v>
+        <v>475302</v>
       </c>
       <c r="R21" t="n">
-        <v>6852836</v>
+        <v>6853363</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118766233</v>
+        <v>118769848</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>79566</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2742,41 +2742,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475181</v>
+        <v>475286</v>
       </c>
       <c r="R22" t="n">
-        <v>6853364</v>
+        <v>6853351</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118762153</v>
+        <v>118766302</v>
       </c>
       <c r="B23" t="n">
         <v>97846</v>
@@ -2865,20 +2865,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474905</v>
+        <v>475179</v>
       </c>
       <c r="R23" t="n">
-        <v>6852851</v>
+        <v>6853360</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2934,7 +2943,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118769866</v>
+        <v>118765116</v>
       </c>
       <c r="B24" t="n">
         <v>97846</v>
@@ -2970,17 +2979,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475289</v>
+        <v>475300</v>
       </c>
       <c r="R24" t="n">
-        <v>6853167</v>
+        <v>6853368</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3036,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118766126</v>
+        <v>118769859</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
+        <v>97750</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3048,41 +3057,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475221</v>
+        <v>475091</v>
       </c>
       <c r="R25" t="n">
-        <v>6853376</v>
+        <v>6853271</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3138,7 +3147,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118769867</v>
+        <v>118769870</v>
       </c>
       <c r="B26" t="n">
         <v>97846</v>
@@ -3178,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475281</v>
+        <v>474936</v>
       </c>
       <c r="R26" t="n">
-        <v>6853098</v>
+        <v>6852846</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3240,7 +3249,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118762495</v>
+        <v>118765086</v>
       </c>
       <c r="B27" t="n">
         <v>97846</v>
@@ -3276,17 +3285,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474949</v>
+        <v>475303</v>
       </c>
       <c r="R27" t="n">
-        <v>6852843</v>
+        <v>6853364</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3330,19 +3339,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118766193</v>
+        <v>118765092</v>
       </c>
       <c r="B28" t="n">
         <v>97846</v>
@@ -3382,13 +3391,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>475229</v>
+        <v>475341</v>
       </c>
       <c r="R28" t="n">
-        <v>6853392</v>
+        <v>6853346</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3444,10 +3453,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118766652</v>
+        <v>118766370</v>
       </c>
       <c r="B29" t="n">
-        <v>79566</v>
+        <v>97846</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3456,41 +3465,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475065</v>
+        <v>475119</v>
       </c>
       <c r="R29" t="n">
-        <v>6853275</v>
+        <v>6853325</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3534,22 +3543,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118769855</v>
+        <v>118769862</v>
       </c>
       <c r="B30" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3558,25 +3567,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3586,10 +3595,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475284</v>
+        <v>475095</v>
       </c>
       <c r="R30" t="n">
-        <v>6853186</v>
+        <v>6853273</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3648,10 +3657,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118769856</v>
+        <v>118769866</v>
       </c>
       <c r="B31" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3660,25 +3669,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3688,10 +3697,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475300</v>
+        <v>475289</v>
       </c>
       <c r="R31" t="n">
-        <v>6853182</v>
+        <v>6853167</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3750,10 +3759,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118764109</v>
+        <v>118762495</v>
       </c>
       <c r="B32" t="n">
-        <v>78129</v>
+        <v>97846</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3762,25 +3771,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3790,13 +3799,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475259</v>
+        <v>474949</v>
       </c>
       <c r="R32" t="n">
-        <v>6853227</v>
+        <v>6852843</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3852,10 +3861,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118766206</v>
+        <v>118765456</v>
       </c>
       <c r="B33" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3864,25 +3873,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3892,10 +3901,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>475201</v>
+        <v>475349</v>
       </c>
       <c r="R33" t="n">
-        <v>6853392</v>
+        <v>6853384</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3928,11 +3937,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3959,10 +3963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118766302</v>
+        <v>118762886</v>
       </c>
       <c r="B34" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3971,50 +3975,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475179</v>
+        <v>474862</v>
       </c>
       <c r="R34" t="n">
-        <v>6853360</v>
+        <v>6852981</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4070,10 +4065,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118766370</v>
+        <v>118766686</v>
       </c>
       <c r="B35" t="n">
-        <v>97846</v>
+        <v>79594</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4082,41 +4077,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475119</v>
+        <v>475054</v>
       </c>
       <c r="R35" t="n">
-        <v>6853325</v>
+        <v>6853272</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4160,22 +4155,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118769846</v>
+        <v>118770271</v>
       </c>
       <c r="B36" t="n">
-        <v>79594</v>
+        <v>57443</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4184,38 +4179,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474860</v>
+        <v>475175</v>
       </c>
       <c r="R36" t="n">
-        <v>6852995</v>
+        <v>6853143</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4274,10 +4277,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118770271</v>
+        <v>118766005</v>
       </c>
       <c r="B37" t="n">
-        <v>57443</v>
+        <v>97846</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,49 +4289,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475175</v>
+        <v>475286</v>
       </c>
       <c r="R37" t="n">
-        <v>6853143</v>
+        <v>6853383</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4384,7 +4379,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118769862</v>
+        <v>118766233</v>
       </c>
       <c r="B38" t="n">
         <v>97846</v>
@@ -4420,17 +4415,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475095</v>
+        <v>475181</v>
       </c>
       <c r="R38" t="n">
-        <v>6853273</v>
+        <v>6853364</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4486,10 +4481,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118769869</v>
+        <v>118766285</v>
       </c>
       <c r="B39" t="n">
-        <v>97846</v>
+        <v>79566</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4498,41 +4493,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474841</v>
+        <v>475155</v>
       </c>
       <c r="R39" t="n">
-        <v>6852986</v>
+        <v>6853357</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4588,10 +4583,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118766023</v>
+        <v>118769852</v>
       </c>
       <c r="B40" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4600,38 +4595,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475261</v>
+        <v>475281</v>
       </c>
       <c r="R40" t="n">
-        <v>6853378</v>
+        <v>6853211</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4690,10 +4685,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118769853</v>
+        <v>118769867</v>
       </c>
       <c r="B41" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4702,25 +4697,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4730,10 +4725,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475286</v>
+        <v>475281</v>
       </c>
       <c r="R41" t="n">
-        <v>6853198</v>
+        <v>6853098</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4792,7 +4787,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118763353</v>
+        <v>118766023</v>
       </c>
       <c r="B42" t="n">
         <v>97846</v>
@@ -4828,17 +4823,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475052</v>
+        <v>475261</v>
       </c>
       <c r="R42" t="n">
-        <v>6853129</v>
+        <v>6853378</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4882,22 +4877,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118769859</v>
+        <v>118769874</v>
       </c>
       <c r="B43" t="n">
-        <v>97750</v>
+        <v>78484</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4906,25 +4901,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4934,10 +4929,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475091</v>
+        <v>475265</v>
       </c>
       <c r="R43" t="n">
-        <v>6853271</v>
+        <v>6853105</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4996,7 +4991,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118765456</v>
+        <v>118769853</v>
       </c>
       <c r="B44" t="n">
         <v>79565</v>
@@ -5032,17 +5027,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475349</v>
+        <v>475286</v>
       </c>
       <c r="R44" t="n">
-        <v>6853384</v>
+        <v>6853198</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5098,10 +5093,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118762755</v>
+        <v>118766297</v>
       </c>
       <c r="B45" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5110,50 +5105,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475026</v>
+        <v>475153</v>
       </c>
       <c r="R45" t="n">
-        <v>6852933</v>
+        <v>6853357</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5197,19 +5183,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118766005</v>
+        <v>118769865</v>
       </c>
       <c r="B46" t="n">
         <v>97846</v>
@@ -5245,17 +5231,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475286</v>
+        <v>475295</v>
       </c>
       <c r="R46" t="n">
-        <v>6853383</v>
+        <v>6853180</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5311,7 +5297,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118765071</v>
+        <v>118766412</v>
       </c>
       <c r="B47" t="n">
         <v>97846</v>
@@ -5347,14 +5333,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475339</v>
+        <v>475111</v>
       </c>
       <c r="R47" t="n">
-        <v>6853351</v>
+        <v>6853306</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5401,22 +5387,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118769848</v>
+        <v>118762755</v>
       </c>
       <c r="B48" t="n">
-        <v>79566</v>
+        <v>97846</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5425,41 +5411,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475286</v>
+        <v>475026</v>
       </c>
       <c r="R48" t="n">
-        <v>6853351</v>
+        <v>6852933</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5503,22 +5498,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118766285</v>
+        <v>118769847</v>
       </c>
       <c r="B49" t="n">
-        <v>79566</v>
+        <v>97867</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5527,41 +5522,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475155</v>
+        <v>474904</v>
       </c>
       <c r="R49" t="n">
-        <v>6853357</v>
+        <v>6852836</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5617,7 +5612,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118766412</v>
+        <v>118766206</v>
       </c>
       <c r="B50" t="n">
         <v>97846</v>
@@ -5657,13 +5652,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475111</v>
+        <v>475201</v>
       </c>
       <c r="R50" t="n">
-        <v>6853306</v>
+        <v>6853392</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5693,6 +5688,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5719,7 +5719,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118765086</v>
+        <v>118769869</v>
       </c>
       <c r="B51" t="n">
         <v>97846</v>
@@ -5755,17 +5755,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475303</v>
+        <v>474841</v>
       </c>
       <c r="R51" t="n">
-        <v>6853364</v>
+        <v>6852986</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118769874</v>
+        <v>118762626</v>
       </c>
       <c r="B52" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5833,41 +5833,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475265</v>
+        <v>474988</v>
       </c>
       <c r="R52" t="n">
-        <v>6853105</v>
+        <v>6852930</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5911,12 +5911,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118769873</v>
+        <v>118762495</v>
       </c>
       <c r="B2" t="n">
-        <v>56272</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208260</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474840</v>
+        <v>474949</v>
       </c>
       <c r="R2" t="n">
-        <v>6852984</v>
+        <v>6852843</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118763114</v>
+        <v>118765092</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474930</v>
+        <v>475341</v>
       </c>
       <c r="R3" t="n">
-        <v>6853098</v>
+        <v>6853346</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118769846</v>
+        <v>118763353</v>
       </c>
       <c r="B4" t="n">
-        <v>79594</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474860</v>
+        <v>475052</v>
       </c>
       <c r="R4" t="n">
-        <v>6852995</v>
+        <v>6853129</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118769860</v>
+        <v>118769866</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475001</v>
+        <v>475289</v>
       </c>
       <c r="R5" t="n">
-        <v>6852915</v>
+        <v>6853167</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118765071</v>
+        <v>118769853</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>79572</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,41 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475339</v>
+        <v>475286</v>
       </c>
       <c r="R6" t="n">
-        <v>6853351</v>
+        <v>6853198</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118765546</v>
+        <v>118762755</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,41 +1197,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475240</v>
+        <v>475026</v>
       </c>
       <c r="R7" t="n">
-        <v>6853164</v>
+        <v>6852933</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118764109</v>
+        <v>118764888</v>
       </c>
       <c r="B8" t="n">
-        <v>78129</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475259</v>
+        <v>475321</v>
       </c>
       <c r="R8" t="n">
-        <v>6853227</v>
+        <v>6853346</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118763353</v>
+        <v>118769873</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>56272</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,41 +1410,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>208260</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475052</v>
+        <v>474840</v>
       </c>
       <c r="R9" t="n">
-        <v>6853129</v>
+        <v>6852984</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1484,22 +1488,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118764888</v>
+        <v>118769855</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>79572</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,41 +1512,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475321</v>
+        <v>475284</v>
       </c>
       <c r="R10" t="n">
-        <v>6853346</v>
+        <v>6853186</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1586,22 +1590,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118769856</v>
+        <v>118766686</v>
       </c>
       <c r="B11" t="n">
-        <v>79565</v>
+        <v>79601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,41 +1614,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475300</v>
+        <v>475054</v>
       </c>
       <c r="R11" t="n">
-        <v>6853182</v>
+        <v>6853272</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118766126</v>
+        <v>118766206</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475221</v>
+        <v>475201</v>
       </c>
       <c r="R12" t="n">
-        <v>6853376</v>
+        <v>6853392</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,6 +1780,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118769861</v>
+        <v>118766005</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,17 +1847,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475079</v>
+        <v>475286</v>
       </c>
       <c r="R13" t="n">
-        <v>6853115</v>
+        <v>6853383</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1878,11 +1887,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118766394</v>
+        <v>118765086</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,13 +1953,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475130</v>
+        <v>475303</v>
       </c>
       <c r="R14" t="n">
-        <v>6853328</v>
+        <v>6853364</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2011,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118762153</v>
+        <v>118769867</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,17 +2051,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474905</v>
+        <v>475281</v>
       </c>
       <c r="R15" t="n">
-        <v>6852851</v>
+        <v>6853098</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2101,22 +2105,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118769844</v>
+        <v>118769848</v>
       </c>
       <c r="B16" t="n">
-        <v>90469</v>
+        <v>79573</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,25 +2129,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474897</v>
+        <v>475286</v>
       </c>
       <c r="R16" t="n">
-        <v>6852835</v>
+        <v>6853351</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2215,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118769855</v>
+        <v>118763114</v>
       </c>
       <c r="B17" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2251,17 +2255,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475284</v>
+        <v>474930</v>
       </c>
       <c r="R17" t="n">
-        <v>6853186</v>
+        <v>6853098</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2305,22 +2309,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118766193</v>
+        <v>118769861</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,17 +2357,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475229</v>
+        <v>475079</v>
       </c>
       <c r="R18" t="n">
-        <v>6853392</v>
+        <v>6853115</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2393,6 +2397,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2407,22 +2416,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118766652</v>
+        <v>118769874</v>
       </c>
       <c r="B19" t="n">
-        <v>79566</v>
+        <v>78491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,37 +2444,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475065</v>
+        <v>475265</v>
       </c>
       <c r="R19" t="n">
-        <v>6853275</v>
+        <v>6853105</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2524,7 +2533,7 @@
         <v>118766078</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2628,10 +2637,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118769863</v>
+        <v>118769846</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
+        <v>79601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,25 +2649,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2677,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475302</v>
+        <v>474860</v>
       </c>
       <c r="R21" t="n">
-        <v>6853363</v>
+        <v>6852995</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2730,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118769848</v>
+        <v>118769870</v>
       </c>
       <c r="B22" t="n">
-        <v>79566</v>
+        <v>97853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2742,25 +2751,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,10 +2779,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475286</v>
+        <v>474936</v>
       </c>
       <c r="R22" t="n">
-        <v>6853351</v>
+        <v>6852846</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2832,10 +2841,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118766302</v>
+        <v>118766193</v>
       </c>
       <c r="B23" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2865,29 +2874,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475179</v>
+        <v>475229</v>
       </c>
       <c r="R23" t="n">
-        <v>6853360</v>
+        <v>6853392</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118765116</v>
+        <v>118765546</v>
       </c>
       <c r="B24" t="n">
-        <v>97846</v>
+        <v>79572</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,41 +2955,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475300</v>
+        <v>475240</v>
       </c>
       <c r="R24" t="n">
-        <v>6853368</v>
+        <v>6853164</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3033,22 +3033,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118769859</v>
+        <v>118769852</v>
       </c>
       <c r="B25" t="n">
-        <v>97750</v>
+        <v>79572</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,25 +3057,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475091</v>
+        <v>475281</v>
       </c>
       <c r="R25" t="n">
-        <v>6853271</v>
+        <v>6853211</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118769870</v>
+        <v>118769860</v>
       </c>
       <c r="B26" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474936</v>
+        <v>475001</v>
       </c>
       <c r="R26" t="n">
-        <v>6852846</v>
+        <v>6852915</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3223,6 +3223,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3249,10 +3254,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118765086</v>
+        <v>118769869</v>
       </c>
       <c r="B27" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3285,17 +3290,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>475303</v>
+        <v>474841</v>
       </c>
       <c r="R27" t="n">
-        <v>6853364</v>
+        <v>6852986</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3351,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118765092</v>
+        <v>118766233</v>
       </c>
       <c r="B28" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3387,17 +3392,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>475341</v>
+        <v>475181</v>
       </c>
       <c r="R28" t="n">
-        <v>6853346</v>
+        <v>6853364</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3441,22 +3446,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118766370</v>
+        <v>118766652</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>79573</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,41 +3470,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475119</v>
+        <v>475065</v>
       </c>
       <c r="R29" t="n">
-        <v>6853325</v>
+        <v>6853275</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3543,22 +3548,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118769862</v>
+        <v>118770271</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>57443</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3567,38 +3572,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475095</v>
+        <v>475175</v>
       </c>
       <c r="R30" t="n">
-        <v>6853273</v>
+        <v>6853143</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3657,10 +3670,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118769866</v>
+        <v>118762153</v>
       </c>
       <c r="B31" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3693,17 +3706,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475289</v>
+        <v>474905</v>
       </c>
       <c r="R31" t="n">
-        <v>6853167</v>
+        <v>6852851</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3747,22 +3760,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118762495</v>
+        <v>118766370</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3799,13 +3812,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474949</v>
+        <v>475119</v>
       </c>
       <c r="R32" t="n">
-        <v>6852843</v>
+        <v>6853325</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3861,10 +3874,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118765456</v>
+        <v>118762886</v>
       </c>
       <c r="B33" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3897,17 +3910,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>475349</v>
+        <v>474862</v>
       </c>
       <c r="R33" t="n">
-        <v>6853384</v>
+        <v>6852981</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3951,22 +3964,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118762886</v>
+        <v>118769859</v>
       </c>
       <c r="B34" t="n">
-        <v>79565</v>
+        <v>97757</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3975,41 +3988,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474862</v>
+        <v>475091</v>
       </c>
       <c r="R34" t="n">
-        <v>6852981</v>
+        <v>6853271</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4053,22 +4066,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118766686</v>
+        <v>118765116</v>
       </c>
       <c r="B35" t="n">
-        <v>79594</v>
+        <v>97853</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4077,25 +4090,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4105,13 +4118,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475054</v>
+        <v>475300</v>
       </c>
       <c r="R35" t="n">
-        <v>6853272</v>
+        <v>6853368</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4167,10 +4180,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118770271</v>
+        <v>118769844</v>
       </c>
       <c r="B36" t="n">
-        <v>57443</v>
+        <v>90476</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,46 +4192,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475175</v>
+        <v>474897</v>
       </c>
       <c r="R36" t="n">
-        <v>6853143</v>
+        <v>6852835</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4277,10 +4282,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118766005</v>
+        <v>118765456</v>
       </c>
       <c r="B37" t="n">
-        <v>97846</v>
+        <v>79572</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4289,25 +4294,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4317,13 +4322,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475286</v>
+        <v>475349</v>
       </c>
       <c r="R37" t="n">
-        <v>6853383</v>
+        <v>6853384</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4379,10 +4384,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118766233</v>
+        <v>118766285</v>
       </c>
       <c r="B38" t="n">
-        <v>97846</v>
+        <v>79573</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4391,25 +4396,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4419,13 +4424,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475181</v>
+        <v>475155</v>
       </c>
       <c r="R38" t="n">
-        <v>6853364</v>
+        <v>6853357</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4481,10 +4486,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118766285</v>
+        <v>118769863</v>
       </c>
       <c r="B39" t="n">
-        <v>79566</v>
+        <v>97853</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4493,41 +4498,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475155</v>
+        <v>475302</v>
       </c>
       <c r="R39" t="n">
-        <v>6853357</v>
+        <v>6853363</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4583,10 +4588,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118769852</v>
+        <v>118769862</v>
       </c>
       <c r="B40" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4595,25 +4600,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4623,10 +4628,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475281</v>
+        <v>475095</v>
       </c>
       <c r="R40" t="n">
-        <v>6853211</v>
+        <v>6853273</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4685,10 +4690,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118769867</v>
+        <v>118769865</v>
       </c>
       <c r="B41" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4725,10 +4730,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475281</v>
+        <v>475295</v>
       </c>
       <c r="R41" t="n">
-        <v>6853098</v>
+        <v>6853180</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4787,10 +4792,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118766023</v>
+        <v>118766412</v>
       </c>
       <c r="B42" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4827,13 +4832,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475261</v>
+        <v>475111</v>
       </c>
       <c r="R42" t="n">
-        <v>6853378</v>
+        <v>6853306</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4889,10 +4894,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118769874</v>
+        <v>118762626</v>
       </c>
       <c r="B43" t="n">
-        <v>78484</v>
+        <v>97853</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4901,41 +4906,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475265</v>
+        <v>474988</v>
       </c>
       <c r="R43" t="n">
-        <v>6853105</v>
+        <v>6852930</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4979,22 +4984,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118769853</v>
+        <v>118766023</v>
       </c>
       <c r="B44" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5003,38 +5008,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475286</v>
+        <v>475261</v>
       </c>
       <c r="R44" t="n">
-        <v>6853198</v>
+        <v>6853378</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5093,10 +5098,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118766297</v>
+        <v>118769856</v>
       </c>
       <c r="B45" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5129,17 +5134,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475153</v>
+        <v>475300</v>
       </c>
       <c r="R45" t="n">
-        <v>6853357</v>
+        <v>6853182</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5195,10 +5200,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118769865</v>
+        <v>118766297</v>
       </c>
       <c r="B46" t="n">
-        <v>97846</v>
+        <v>79572</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5207,41 +5212,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475295</v>
+        <v>475153</v>
       </c>
       <c r="R46" t="n">
-        <v>6853180</v>
+        <v>6853357</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5297,10 +5302,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118766412</v>
+        <v>118764109</v>
       </c>
       <c r="B47" t="n">
-        <v>97846</v>
+        <v>78136</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5309,38 +5314,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475111</v>
+        <v>475259</v>
       </c>
       <c r="R47" t="n">
-        <v>6853306</v>
+        <v>6853227</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5387,22 +5392,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118762755</v>
+        <v>118766126</v>
       </c>
       <c r="B48" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5432,29 +5437,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475026</v>
+        <v>475221</v>
       </c>
       <c r="R48" t="n">
-        <v>6852933</v>
+        <v>6853376</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5498,22 +5494,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118769847</v>
+        <v>118766302</v>
       </c>
       <c r="B49" t="n">
-        <v>97867</v>
+        <v>97853</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5522,41 +5518,50 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474904</v>
+        <v>475179</v>
       </c>
       <c r="R49" t="n">
-        <v>6852836</v>
+        <v>6853360</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5600,22 +5605,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118766206</v>
+        <v>118766394</v>
       </c>
       <c r="B50" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5652,10 +5657,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475201</v>
+        <v>475130</v>
       </c>
       <c r="R50" t="n">
-        <v>6853392</v>
+        <v>6853328</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5688,11 +5693,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5719,10 +5719,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118769869</v>
+        <v>118765071</v>
       </c>
       <c r="B51" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5755,17 +5755,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474841</v>
+        <v>475339</v>
       </c>
       <c r="R51" t="n">
-        <v>6852986</v>
+        <v>6853351</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5809,22 +5809,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118762626</v>
+        <v>118769847</v>
       </c>
       <c r="B52" t="n">
-        <v>97846</v>
+        <v>97874</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5833,41 +5833,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474988</v>
+        <v>474904</v>
       </c>
       <c r="R52" t="n">
-        <v>6852930</v>
+        <v>6852836</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5911,12 +5911,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -5200,10 +5200,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118766297</v>
+        <v>118766126</v>
       </c>
       <c r="B46" t="n">
-        <v>79572</v>
+        <v>97853</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5212,25 +5212,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475153</v>
+        <v>475221</v>
       </c>
       <c r="R46" t="n">
-        <v>6853357</v>
+        <v>6853376</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5302,10 +5302,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118764109</v>
+        <v>118766302</v>
       </c>
       <c r="B47" t="n">
-        <v>78136</v>
+        <v>97853</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5314,38 +5314,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475259</v>
+        <v>475179</v>
       </c>
       <c r="R47" t="n">
-        <v>6853227</v>
+        <v>6853360</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5404,7 +5413,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118766126</v>
+        <v>118766394</v>
       </c>
       <c r="B48" t="n">
         <v>97853</v>
@@ -5444,10 +5453,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475221</v>
+        <v>475130</v>
       </c>
       <c r="R48" t="n">
-        <v>6853376</v>
+        <v>6853328</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5506,7 +5515,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118766302</v>
+        <v>118765071</v>
       </c>
       <c r="B49" t="n">
         <v>97853</v>
@@ -5539,26 +5548,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475179</v>
+        <v>475339</v>
       </c>
       <c r="R49" t="n">
-        <v>6853360</v>
+        <v>6853351</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5617,10 +5617,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118766394</v>
+        <v>118769847</v>
       </c>
       <c r="B50" t="n">
-        <v>97853</v>
+        <v>97874</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5629,41 +5629,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475130</v>
+        <v>474904</v>
       </c>
       <c r="R50" t="n">
-        <v>6853328</v>
+        <v>6852836</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5719,10 +5719,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118765071</v>
+        <v>118764109</v>
       </c>
       <c r="B51" t="n">
-        <v>97853</v>
+        <v>78136</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5731,25 +5731,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475339</v>
+        <v>475259</v>
       </c>
       <c r="R51" t="n">
-        <v>6853351</v>
+        <v>6853227</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5821,10 +5821,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118769847</v>
+        <v>118766297</v>
       </c>
       <c r="B52" t="n">
-        <v>97874</v>
+        <v>79572</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5833,41 +5833,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474904</v>
+        <v>475153</v>
       </c>
       <c r="R52" t="n">
-        <v>6852836</v>
+        <v>6853357</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118762495</v>
+        <v>118766206</v>
       </c>
       <c r="B2" t="n">
         <v>97853</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474949</v>
+        <v>475201</v>
       </c>
       <c r="R2" t="n">
-        <v>6852843</v>
+        <v>6853392</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +753,11 @@
           <t>2024-07-29</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -765,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118765092</v>
+        <v>118766096</v>
       </c>
       <c r="B3" t="n">
         <v>97853</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475341</v>
+        <v>475291</v>
       </c>
       <c r="R3" t="n">
-        <v>6853346</v>
+        <v>6853381</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118763353</v>
+        <v>118766297</v>
       </c>
       <c r="B4" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +896,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475052</v>
+        <v>475153</v>
       </c>
       <c r="R4" t="n">
-        <v>6853129</v>
+        <v>6853357</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,19 +974,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118769866</v>
+        <v>118766193</v>
       </c>
       <c r="B5" t="n">
         <v>97853</v>
@@ -1017,17 +1022,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475289</v>
+        <v>475229</v>
       </c>
       <c r="R5" t="n">
-        <v>6853167</v>
+        <v>6853392</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118769853</v>
+        <v>118762480</v>
       </c>
       <c r="B6" t="n">
-        <v>79572</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1100,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475286</v>
+        <v>474949</v>
       </c>
       <c r="R6" t="n">
-        <v>6853198</v>
+        <v>6852843</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,19 +1178,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118762755</v>
+        <v>118766394</v>
       </c>
       <c r="B7" t="n">
         <v>97853</v>
@@ -1218,29 +1223,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475026</v>
+        <v>475130</v>
       </c>
       <c r="R7" t="n">
-        <v>6852933</v>
+        <v>6853328</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,19 +1280,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118764888</v>
+        <v>118766023</v>
       </c>
       <c r="B8" t="n">
         <v>97853</v>
@@ -1332,17 +1328,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475321</v>
+        <v>475261</v>
       </c>
       <c r="R8" t="n">
-        <v>6853346</v>
+        <v>6853378</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,12 +1382,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1500,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118769855</v>
+        <v>118764109</v>
       </c>
       <c r="B10" t="n">
-        <v>79572</v>
+        <v>78136</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,37 +1512,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475284</v>
+        <v>475259</v>
       </c>
       <c r="R10" t="n">
-        <v>6853186</v>
+        <v>6853227</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1590,22 +1586,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118766686</v>
+        <v>118766126</v>
       </c>
       <c r="B11" t="n">
-        <v>79601</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475054</v>
+        <v>475221</v>
       </c>
       <c r="R11" t="n">
-        <v>6853272</v>
+        <v>6853376</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118766206</v>
+        <v>118769861</v>
       </c>
       <c r="B12" t="n">
         <v>97853</v>
@@ -1740,17 +1736,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475201</v>
+        <v>475079</v>
       </c>
       <c r="R12" t="n">
-        <v>6853392</v>
+        <v>6853115</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1784,7 +1780,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1811,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118766005</v>
+        <v>118769867</v>
       </c>
       <c r="B13" t="n">
         <v>97853</v>
@@ -1847,17 +1843,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475286</v>
+        <v>475281</v>
       </c>
       <c r="R13" t="n">
-        <v>6853383</v>
+        <v>6853098</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1913,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118765086</v>
+        <v>118766370</v>
       </c>
       <c r="B14" t="n">
         <v>97853</v>
@@ -1949,17 +1945,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475303</v>
+        <v>475119</v>
       </c>
       <c r="R14" t="n">
-        <v>6853364</v>
+        <v>6853325</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2003,19 +1999,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118769867</v>
+        <v>118765086</v>
       </c>
       <c r="B15" t="n">
         <v>97853</v>
@@ -2051,17 +2047,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475281</v>
+        <v>475303</v>
       </c>
       <c r="R15" t="n">
-        <v>6853098</v>
+        <v>6853364</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2117,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118769848</v>
+        <v>118765116</v>
       </c>
       <c r="B16" t="n">
-        <v>79573</v>
+        <v>97853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,41 +2125,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475286</v>
+        <v>475300</v>
       </c>
       <c r="R16" t="n">
-        <v>6853351</v>
+        <v>6853368</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2219,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118763114</v>
+        <v>118765546</v>
       </c>
       <c r="B17" t="n">
         <v>79572</v>
@@ -2259,13 +2255,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474930</v>
+        <v>475240</v>
       </c>
       <c r="R17" t="n">
-        <v>6853098</v>
+        <v>6853164</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2321,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118769861</v>
+        <v>118765092</v>
       </c>
       <c r="B18" t="n">
         <v>97853</v>
@@ -2357,17 +2353,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475079</v>
+        <v>475341</v>
       </c>
       <c r="R18" t="n">
-        <v>6853115</v>
+        <v>6853346</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2397,11 +2393,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2416,22 +2407,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118769874</v>
+        <v>118769870</v>
       </c>
       <c r="B19" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,25 +2431,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475265</v>
+        <v>474936</v>
       </c>
       <c r="R19" t="n">
-        <v>6853105</v>
+        <v>6852846</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2530,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118766078</v>
+        <v>118766686</v>
       </c>
       <c r="B20" t="n">
-        <v>97853</v>
+        <v>79601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,41 +2533,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475291</v>
+        <v>475054</v>
       </c>
       <c r="R20" t="n">
-        <v>6853381</v>
+        <v>6853272</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2606,11 +2597,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>15-tal individer</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2625,22 +2611,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118769846</v>
+        <v>118769859</v>
       </c>
       <c r="B21" t="n">
-        <v>79601</v>
+        <v>97757</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>220093</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2677,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474860</v>
+        <v>475091</v>
       </c>
       <c r="R21" t="n">
-        <v>6852995</v>
+        <v>6853271</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2739,7 +2725,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118769870</v>
+        <v>118769865</v>
       </c>
       <c r="B22" t="n">
         <v>97853</v>
@@ -2779,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474936</v>
+        <v>475295</v>
       </c>
       <c r="R22" t="n">
-        <v>6852846</v>
+        <v>6853180</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2841,7 +2827,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118766193</v>
+        <v>118766412</v>
       </c>
       <c r="B23" t="n">
         <v>97853</v>
@@ -2877,17 +2863,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475229</v>
+        <v>475111</v>
       </c>
       <c r="R23" t="n">
-        <v>6853392</v>
+        <v>6853306</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2931,22 +2917,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118765546</v>
+        <v>118762153</v>
       </c>
       <c r="B24" t="n">
-        <v>79572</v>
+        <v>97853</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,25 +2941,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,13 +2969,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475240</v>
+        <v>474905</v>
       </c>
       <c r="R24" t="n">
-        <v>6853164</v>
+        <v>6852851</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3045,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118769852</v>
+        <v>118769846</v>
       </c>
       <c r="B25" t="n">
-        <v>79572</v>
+        <v>79601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,25 +3043,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475281</v>
+        <v>474860</v>
       </c>
       <c r="R25" t="n">
-        <v>6853211</v>
+        <v>6852995</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3147,7 +3133,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118769860</v>
+        <v>118763353</v>
       </c>
       <c r="B26" t="n">
         <v>97853</v>
@@ -3183,17 +3169,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475001</v>
+        <v>475052</v>
       </c>
       <c r="R26" t="n">
-        <v>6852915</v>
+        <v>6853129</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3223,11 +3209,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3242,19 +3223,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118769869</v>
+        <v>118766233</v>
       </c>
       <c r="B27" t="n">
         <v>97853</v>
@@ -3290,17 +3271,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474841</v>
+        <v>475181</v>
       </c>
       <c r="R27" t="n">
-        <v>6852986</v>
+        <v>6853364</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3356,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118766233</v>
+        <v>118762886</v>
       </c>
       <c r="B28" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,38 +3349,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>475181</v>
+        <v>474862</v>
       </c>
       <c r="R28" t="n">
-        <v>6853364</v>
+        <v>6852981</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3446,22 +3427,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118766652</v>
+        <v>118769852</v>
       </c>
       <c r="B29" t="n">
-        <v>79573</v>
+        <v>79572</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3474,37 +3455,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475065</v>
+        <v>475281</v>
       </c>
       <c r="R29" t="n">
-        <v>6853275</v>
+        <v>6853211</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3670,7 +3651,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118762153</v>
+        <v>118765071</v>
       </c>
       <c r="B31" t="n">
         <v>97853</v>
@@ -3710,13 +3691,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474905</v>
+        <v>475339</v>
       </c>
       <c r="R31" t="n">
-        <v>6852851</v>
+        <v>6853351</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3772,10 +3753,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118766370</v>
+        <v>118766285</v>
       </c>
       <c r="B32" t="n">
-        <v>97853</v>
+        <v>79573</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3784,41 +3765,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475119</v>
+        <v>475155</v>
       </c>
       <c r="R32" t="n">
-        <v>6853325</v>
+        <v>6853357</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3862,19 +3843,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118762886</v>
+        <v>118769856</v>
       </c>
       <c r="B33" t="n">
         <v>79572</v>
@@ -3910,17 +3891,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474862</v>
+        <v>475300</v>
       </c>
       <c r="R33" t="n">
-        <v>6852981</v>
+        <v>6853182</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3964,22 +3945,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118769859</v>
+        <v>118769863</v>
       </c>
       <c r="B34" t="n">
-        <v>97757</v>
+        <v>97853</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3988,25 +3969,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4016,10 +3997,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475091</v>
+        <v>475302</v>
       </c>
       <c r="R34" t="n">
-        <v>6853271</v>
+        <v>6853363</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4078,10 +4059,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118765116</v>
+        <v>118769855</v>
       </c>
       <c r="B35" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4090,41 +4071,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475300</v>
+        <v>475284</v>
       </c>
       <c r="R35" t="n">
-        <v>6853368</v>
+        <v>6853186</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4180,10 +4161,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118769844</v>
+        <v>118762755</v>
       </c>
       <c r="B36" t="n">
-        <v>90476</v>
+        <v>97853</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4192,41 +4173,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474897</v>
+        <v>475026</v>
       </c>
       <c r="R36" t="n">
-        <v>6852835</v>
+        <v>6852933</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4270,22 +4260,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118765456</v>
+        <v>118764888</v>
       </c>
       <c r="B37" t="n">
-        <v>79572</v>
+        <v>97853</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4294,41 +4284,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475349</v>
+        <v>475321</v>
       </c>
       <c r="R37" t="n">
-        <v>6853384</v>
+        <v>6853346</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4372,22 +4362,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118766285</v>
+        <v>118769853</v>
       </c>
       <c r="B38" t="n">
-        <v>79573</v>
+        <v>79572</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4400,37 +4390,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475155</v>
+        <v>475286</v>
       </c>
       <c r="R38" t="n">
-        <v>6853357</v>
+        <v>6853198</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4486,10 +4476,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118769863</v>
+        <v>118765456</v>
       </c>
       <c r="B39" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4498,41 +4488,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475302</v>
+        <v>475349</v>
       </c>
       <c r="R39" t="n">
-        <v>6853363</v>
+        <v>6853384</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4588,10 +4578,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118769862</v>
+        <v>118769847</v>
       </c>
       <c r="B40" t="n">
-        <v>97853</v>
+        <v>97874</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4600,25 +4590,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4628,10 +4618,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475095</v>
+        <v>474904</v>
       </c>
       <c r="R40" t="n">
-        <v>6853273</v>
+        <v>6852836</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4690,7 +4680,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118769865</v>
+        <v>118762626</v>
       </c>
       <c r="B41" t="n">
         <v>97853</v>
@@ -4726,17 +4716,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475295</v>
+        <v>474988</v>
       </c>
       <c r="R41" t="n">
-        <v>6853180</v>
+        <v>6852930</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4780,19 +4770,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118766412</v>
+        <v>118769860</v>
       </c>
       <c r="B42" t="n">
         <v>97853</v>
@@ -4828,17 +4818,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475111</v>
+        <v>475001</v>
       </c>
       <c r="R42" t="n">
-        <v>6853306</v>
+        <v>6852915</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4868,6 +4858,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4894,7 +4889,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118762626</v>
+        <v>118769869</v>
       </c>
       <c r="B43" t="n">
         <v>97853</v>
@@ -4930,17 +4925,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474988</v>
+        <v>474841</v>
       </c>
       <c r="R43" t="n">
-        <v>6852930</v>
+        <v>6852986</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4984,22 +4979,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118766023</v>
+        <v>118769874</v>
       </c>
       <c r="B44" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5008,38 +5003,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475261</v>
+        <v>475265</v>
       </c>
       <c r="R44" t="n">
-        <v>6853378</v>
+        <v>6853105</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5098,10 +5093,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118769856</v>
+        <v>118766302</v>
       </c>
       <c r="B45" t="n">
-        <v>79572</v>
+        <v>97853</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5110,41 +5105,50 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475300</v>
+        <v>475179</v>
       </c>
       <c r="R45" t="n">
-        <v>6853182</v>
+        <v>6853360</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5188,19 +5192,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118766126</v>
+        <v>118769866</v>
       </c>
       <c r="B46" t="n">
         <v>97853</v>
@@ -5236,17 +5240,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475221</v>
+        <v>475289</v>
       </c>
       <c r="R46" t="n">
-        <v>6853376</v>
+        <v>6853167</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5302,10 +5306,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118766302</v>
+        <v>118769848</v>
       </c>
       <c r="B47" t="n">
-        <v>97853</v>
+        <v>79573</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5314,50 +5318,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475179</v>
+        <v>475286</v>
       </c>
       <c r="R47" t="n">
-        <v>6853360</v>
+        <v>6853351</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5401,19 +5396,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118766394</v>
+        <v>118766005</v>
       </c>
       <c r="B48" t="n">
         <v>97853</v>
@@ -5453,13 +5448,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475130</v>
+        <v>475286</v>
       </c>
       <c r="R48" t="n">
-        <v>6853328</v>
+        <v>6853383</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5515,7 +5510,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118765071</v>
+        <v>118769862</v>
       </c>
       <c r="B49" t="n">
         <v>97853</v>
@@ -5551,17 +5546,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475339</v>
+        <v>475095</v>
       </c>
       <c r="R49" t="n">
-        <v>6853351</v>
+        <v>6853273</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5605,22 +5600,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118769847</v>
+        <v>118766652</v>
       </c>
       <c r="B50" t="n">
-        <v>97874</v>
+        <v>79573</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5629,41 +5624,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474904</v>
+        <v>475065</v>
       </c>
       <c r="R50" t="n">
-        <v>6852836</v>
+        <v>6853275</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5719,10 +5714,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118764109</v>
+        <v>118763114</v>
       </c>
       <c r="B51" t="n">
-        <v>78136</v>
+        <v>79572</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5735,21 +5730,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5759,13 +5754,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475259</v>
+        <v>474930</v>
       </c>
       <c r="R51" t="n">
-        <v>6853227</v>
+        <v>6853098</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5821,10 +5816,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118766297</v>
+        <v>118769844</v>
       </c>
       <c r="B52" t="n">
-        <v>79572</v>
+        <v>90476</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5833,41 +5828,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475153</v>
+        <v>474897</v>
       </c>
       <c r="R52" t="n">
-        <v>6853357</v>
+        <v>6852835</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118770271</v>
+        <v>118764109</v>
       </c>
       <c r="B2" t="n">
-        <v>57445</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475175</v>
+        <v>475259</v>
       </c>
       <c r="R2" t="n">
-        <v>6853143</v>
+        <v>6853227</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118765456</v>
+        <v>118763764</v>
       </c>
       <c r="B3" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475349</v>
+        <v>475199</v>
       </c>
       <c r="R3" t="n">
-        <v>6853384</v>
+        <v>6853110</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118765546</v>
+        <v>118766285</v>
       </c>
       <c r="B4" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475240</v>
+        <v>475155</v>
       </c>
       <c r="R4" t="n">
-        <v>6853164</v>
+        <v>6853357</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,65 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118766233</v>
+        <v>118766652</v>
       </c>
       <c r="B5" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475181</v>
+        <v>475065</v>
       </c>
       <c r="R5" t="n">
-        <v>6853364</v>
+        <v>6853275</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118766297</v>
+        <v>118769848</v>
       </c>
       <c r="B6" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475153</v>
+        <v>475286</v>
       </c>
       <c r="R6" t="n">
-        <v>6853357</v>
+        <v>6853351</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118769861</v>
+        <v>118769849</v>
       </c>
       <c r="B7" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475079</v>
+        <v>475179</v>
       </c>
       <c r="R7" t="n">
-        <v>6853115</v>
+        <v>6853119</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1269,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,50 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118766023</v>
+        <v>118769844</v>
       </c>
       <c r="B8" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475261</v>
+        <v>474897</v>
       </c>
       <c r="R8" t="n">
-        <v>6853378</v>
+        <v>6852835</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1402,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118766193</v>
+        <v>118769874</v>
       </c>
       <c r="B9" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475229</v>
+        <v>475265</v>
       </c>
       <c r="R9" t="n">
-        <v>6853392</v>
+        <v>6853105</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1492,12 +1439,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1507,12 +1454,7 @@
         <v>118762886</v>
       </c>
       <c r="B10" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118766285</v>
+        <v>118763114</v>
       </c>
       <c r="B11" t="n">
-        <v>79575</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1622,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475155</v>
+        <v>474930</v>
       </c>
       <c r="R11" t="n">
-        <v>6853357</v>
+        <v>6853098</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,65 +1633,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118769860</v>
+        <v>118763770</v>
       </c>
       <c r="B12" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475001</v>
+        <v>475208</v>
       </c>
       <c r="R12" t="n">
-        <v>6852915</v>
+        <v>6853108</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1784,11 +1716,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1803,65 +1730,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118764888</v>
+        <v>118765456</v>
       </c>
       <c r="B13" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475321</v>
+        <v>475349</v>
       </c>
       <c r="R13" t="n">
-        <v>6853346</v>
+        <v>6853384</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1905,27 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118763114</v>
+        <v>118765546</v>
       </c>
       <c r="B14" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,17 +1870,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474930</v>
+        <v>475240</v>
       </c>
       <c r="R14" t="n">
-        <v>6853098</v>
+        <v>6853164</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2019,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118769874</v>
+        <v>118766297</v>
       </c>
       <c r="B15" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2035,37 +1947,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475265</v>
+        <v>475153</v>
       </c>
       <c r="R15" t="n">
-        <v>6853105</v>
+        <v>6853357</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2121,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118769855</v>
+        <v>118766672</v>
       </c>
       <c r="B16" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2157,17 +2064,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475284</v>
+        <v>475054</v>
       </c>
       <c r="R16" t="n">
-        <v>6853186</v>
+        <v>6853284</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2223,53 +2130,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118766078</v>
+        <v>118769852</v>
       </c>
       <c r="B17" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475291</v>
+        <v>475281</v>
       </c>
       <c r="R17" t="n">
-        <v>6853381</v>
+        <v>6853211</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2299,11 +2201,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>15-tal individer</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2318,49 +2215,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118769863</v>
+        <v>118769853</v>
       </c>
       <c r="B18" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2370,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475302</v>
+        <v>475286</v>
       </c>
       <c r="R18" t="n">
-        <v>6853363</v>
+        <v>6853198</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2432,53 +2324,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118765116</v>
+        <v>118769855</v>
       </c>
       <c r="B19" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475300</v>
+        <v>475284</v>
       </c>
       <c r="R19" t="n">
-        <v>6853368</v>
+        <v>6853186</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2537,12 +2424,7 @@
         <v>118769856</v>
       </c>
       <c r="B20" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,50 +2518,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118762626</v>
+        <v>118766686</v>
       </c>
       <c r="B21" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474988</v>
+        <v>475054</v>
       </c>
       <c r="R21" t="n">
-        <v>6852930</v>
+        <v>6853272</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2726,65 +2603,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118766394</v>
+        <v>118769846</v>
       </c>
       <c r="B22" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475130</v>
+        <v>474860</v>
       </c>
       <c r="R22" t="n">
-        <v>6853328</v>
+        <v>6852995</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2840,53 +2712,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118762495</v>
+        <v>118769876</v>
       </c>
       <c r="B23" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474949</v>
+        <v>475176</v>
       </c>
       <c r="R23" t="n">
-        <v>6852843</v>
+        <v>6853122</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2930,65 +2797,68 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118766126</v>
+        <v>118770271</v>
       </c>
       <c r="B24" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475221</v>
+        <v>475175</v>
       </c>
       <c r="R24" t="n">
-        <v>6853376</v>
+        <v>6853143</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3044,53 +2914,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118764109</v>
+        <v>118769873</v>
       </c>
       <c r="B25" t="n">
-        <v>78138</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>208260</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475259</v>
+        <v>474840</v>
       </c>
       <c r="R25" t="n">
-        <v>6853227</v>
+        <v>6852984</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3134,65 +2999,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118769870</v>
+        <v>118766502</v>
       </c>
       <c r="B26" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474936</v>
+        <v>475093</v>
       </c>
       <c r="R26" t="n">
-        <v>6852846</v>
+        <v>6853257</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3236,65 +3096,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118766005</v>
+        <v>118769859</v>
       </c>
       <c r="B27" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>475286</v>
+        <v>475091</v>
       </c>
       <c r="R27" t="n">
-        <v>6853383</v>
+        <v>6853271</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3350,15 +3205,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118765086</v>
+        <v>118762153</v>
       </c>
       <c r="B28" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3386,17 +3236,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>475303</v>
+        <v>474905</v>
       </c>
       <c r="R28" t="n">
-        <v>6853364</v>
+        <v>6852851</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3440,27 +3290,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118762153</v>
+        <v>118762480</v>
       </c>
       <c r="B29" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3488,14 +3333,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474905</v>
+        <v>474949</v>
       </c>
       <c r="R29" t="n">
-        <v>6852851</v>
+        <v>6852843</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3554,15 +3399,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118769866</v>
+        <v>118762626</v>
       </c>
       <c r="B30" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,17 +3430,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475289</v>
+        <v>474988</v>
       </c>
       <c r="R30" t="n">
-        <v>6853167</v>
+        <v>6852930</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3644,65 +3484,69 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118769859</v>
+        <v>118762755</v>
       </c>
       <c r="B31" t="n">
-        <v>97762</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475091</v>
+        <v>475026</v>
       </c>
       <c r="R31" t="n">
-        <v>6853271</v>
+        <v>6852933</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3746,27 +3590,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118769867</v>
+        <v>118763353</v>
       </c>
       <c r="B32" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3794,17 +3633,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475281</v>
+        <v>475052</v>
       </c>
       <c r="R32" t="n">
-        <v>6853098</v>
+        <v>6853129</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3848,27 +3687,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118765071</v>
+        <v>118763600</v>
       </c>
       <c r="B33" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3896,17 +3730,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>475339</v>
+        <v>475143</v>
       </c>
       <c r="R33" t="n">
-        <v>6853351</v>
+        <v>6853105</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3962,53 +3796,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118769852</v>
+        <v>118763943</v>
       </c>
       <c r="B34" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475281</v>
+        <v>475284</v>
       </c>
       <c r="R34" t="n">
-        <v>6853211</v>
+        <v>6853102</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4052,27 +3881,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118769865</v>
+        <v>118764888</v>
       </c>
       <c r="B35" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4100,17 +3924,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475295</v>
+        <v>475321</v>
       </c>
       <c r="R35" t="n">
-        <v>6853180</v>
+        <v>6853346</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4154,27 +3978,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118765092</v>
+        <v>118765071</v>
       </c>
       <c r="B36" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4202,14 +4021,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475341</v>
+        <v>475339</v>
       </c>
       <c r="R36" t="n">
-        <v>6853346</v>
+        <v>6853351</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4268,15 +4087,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118769869</v>
+        <v>118765086</v>
       </c>
       <c r="B37" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4304,17 +4118,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474841</v>
+        <v>475303</v>
       </c>
       <c r="R37" t="n">
-        <v>6852986</v>
+        <v>6853364</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4370,53 +4184,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118769844</v>
+        <v>118765092</v>
       </c>
       <c r="B38" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474897</v>
+        <v>475341</v>
       </c>
       <c r="R38" t="n">
-        <v>6852835</v>
+        <v>6853346</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4460,65 +4269,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118766686</v>
+        <v>118765116</v>
       </c>
       <c r="B39" t="n">
-        <v>79603</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475054</v>
+        <v>475300</v>
       </c>
       <c r="R39" t="n">
-        <v>6853272</v>
+        <v>6853368</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4574,15 +4378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118766302</v>
+        <v>118765189</v>
       </c>
       <c r="B40" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4607,26 +4406,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475179</v>
+        <v>475342</v>
       </c>
       <c r="R40" t="n">
-        <v>6853360</v>
+        <v>6853462</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4685,15 +4475,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118766370</v>
+        <v>118765796</v>
       </c>
       <c r="B41" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4721,14 +4506,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475119</v>
+        <v>475325</v>
       </c>
       <c r="R41" t="n">
-        <v>6853325</v>
+        <v>6853434</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4775,65 +4560,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118769848</v>
+        <v>118766005</v>
       </c>
       <c r="B42" t="n">
-        <v>79575</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
         <v>475286</v>
       </c>
       <c r="R42" t="n">
-        <v>6853351</v>
+        <v>6853383</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4889,50 +4669,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118769846</v>
+        <v>118766023</v>
       </c>
       <c r="B43" t="n">
-        <v>79603</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474860</v>
+        <v>475261</v>
       </c>
       <c r="R43" t="n">
-        <v>6852995</v>
+        <v>6853378</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4991,15 +4766,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118766206</v>
+        <v>118766078</v>
       </c>
       <c r="B44" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5027,17 +4797,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475201</v>
+        <v>475291</v>
       </c>
       <c r="R44" t="n">
-        <v>6853392</v>
+        <v>6853381</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5071,7 +4841,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>15-tal individer</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5086,65 +4856,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118769847</v>
+        <v>118766126</v>
       </c>
       <c r="B45" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474904</v>
+        <v>475221</v>
       </c>
       <c r="R45" t="n">
-        <v>6852836</v>
+        <v>6853376</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5200,53 +4965,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118766652</v>
+        <v>118766193</v>
       </c>
       <c r="B46" t="n">
-        <v>79575</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475065</v>
+        <v>475229</v>
       </c>
       <c r="R46" t="n">
-        <v>6853275</v>
+        <v>6853392</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5290,27 +5050,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118769862</v>
+        <v>118766206</v>
       </c>
       <c r="B47" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5338,17 +5093,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475095</v>
+        <v>475201</v>
       </c>
       <c r="R47" t="n">
-        <v>6853273</v>
+        <v>6853392</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5378,6 +5133,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5404,53 +5164,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118769873</v>
+        <v>118766233</v>
       </c>
       <c r="B48" t="n">
-        <v>56274</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>208260</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474840</v>
+        <v>475181</v>
       </c>
       <c r="R48" t="n">
-        <v>6852984</v>
+        <v>6853364</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5506,15 +5261,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118763353</v>
+        <v>118766302</v>
       </c>
       <c r="B49" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5539,17 +5289,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475052</v>
+        <v>475179</v>
       </c>
       <c r="R49" t="n">
-        <v>6853129</v>
+        <v>6853360</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5608,53 +5367,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118769853</v>
+        <v>118766365</v>
       </c>
       <c r="B50" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475286</v>
+        <v>475137</v>
       </c>
       <c r="R50" t="n">
-        <v>6853198</v>
+        <v>6853331</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5710,15 +5464,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118766412</v>
+        <v>118766370</v>
       </c>
       <c r="B51" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5746,14 +5495,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen (Sjöarbergsvallen), Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475111</v>
+        <v>475119</v>
       </c>
       <c r="R51" t="n">
-        <v>6853306</v>
+        <v>6853325</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5800,27 +5549,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118762755</v>
+        <v>118766394</v>
       </c>
       <c r="B52" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5845,29 +5589,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hälltjärnen (Hälltjärnen), Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475026</v>
+        <v>475130</v>
       </c>
       <c r="R52" t="n">
-        <v>6852933</v>
+        <v>6853328</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5911,15 +5646,1577 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>118766412</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>475111</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6853306</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>118766545</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>475103</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6853253</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
+      <c r="AX54" t="inlineStr">
         <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY52" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>118766589</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>475060</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6853289</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>118766595</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>475079</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6853256</v>
+      </c>
+      <c r="S56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>118769860</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>475001</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6852915</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>118769861</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>475079</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6853115</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>118769862</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>475095</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6853273</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>118769863</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>475302</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6853363</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>118769865</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>475295</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6853180</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>118769866</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>475289</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6853167</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>118769867</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>475281</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6853098</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>118769869</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>474841</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6852986</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>118769870</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>474936</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6852846</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>118769871</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>475275</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6853238</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>118769847</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>474904</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6852836</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>118763737</v>
+      </c>
+      <c r="B68" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>475209</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6853105</v>
+      </c>
+      <c r="S68" t="n">
+        <v>20</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118764109</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118763764</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766285</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766652</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769848</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769849</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769844</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769874</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762886</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118763114</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118763770</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765456</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765546</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766297</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766672</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769852</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769853</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769855</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769856</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766686</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769846</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769876</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2911,6 +3026,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118770271</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3008,6 +3128,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769873</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3105,6 +3230,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766502</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3202,6 +3332,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769859</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3299,6 +3434,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762153</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3396,6 +3536,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762480</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3493,6 +3638,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762626</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3599,6 +3749,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762755</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3696,6 +3851,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118763353</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3793,6 +3953,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118763600</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3890,6 +4055,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118763943</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3987,6 +4157,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118764888</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4084,6 +4259,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765071</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4181,6 +4361,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765086</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4278,6 +4463,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765092</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4375,6 +4565,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765116</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4472,6 +4667,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765189</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4569,6 +4769,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765796</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4666,6 +4871,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766005</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4763,6 +4973,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766023</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4865,6 +5080,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766078</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4962,6 +5182,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766126</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5059,6 +5284,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766193</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5161,6 +5391,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766206</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5258,6 +5493,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766233</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5364,6 +5604,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766302</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5461,6 +5706,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766365</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5558,6 +5808,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766370</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5655,6 +5910,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766394</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5752,6 +6012,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766412</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5849,6 +6114,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766545</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5946,6 +6216,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766589</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6043,6 +6318,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118766595</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6145,6 +6425,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769860</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6247,6 +6532,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769861</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6344,6 +6634,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769862</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6441,6 +6736,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769863</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6538,6 +6838,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769865</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6635,6 +6940,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769866</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6732,6 +7042,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769867</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6829,6 +7144,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769869</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6926,6 +7246,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769870</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7023,6 +7348,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769871</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7120,6 +7450,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769847</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7217,8 +7552,82 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118763737</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ68"/>
+  <dimension ref="A1:AZ115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118764109</v>
+        <v>135601119</v>
       </c>
       <c r="B2" t="n">
-        <v>78993</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475259</v>
+        <v>474901</v>
       </c>
       <c r="R2" t="n">
-        <v>6853227</v>
+        <v>6853068</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,16 +776,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118764109</t>
+          <t>https://artportalen.se/Sighting/135601119</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118763764</v>
+        <v>118764109</v>
       </c>
       <c r="B3" t="n">
-        <v>80433</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475199</v>
+        <v>475259</v>
       </c>
       <c r="R3" t="n">
-        <v>6853110</v>
+        <v>6853227</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,16 +878,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118763764</t>
+          <t>https://artportalen.se/Sighting/118764109</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118766285</v>
+        <v>135600489</v>
       </c>
       <c r="B4" t="n">
-        <v>80433</v>
+        <v>92027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475155</v>
+        <v>474926</v>
       </c>
       <c r="R4" t="n">
-        <v>6853357</v>
+        <v>6853016</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,24 +969,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766285</t>
+          <t>https://artportalen.se/Sighting/135600489</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118766652</v>
+        <v>118763764</v>
       </c>
       <c r="B5" t="n">
         <v>80433</v>
@@ -1017,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475065</v>
+        <v>475199</v>
       </c>
       <c r="R5" t="n">
-        <v>6853275</v>
+        <v>6853110</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,24 +1071,24 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766652</t>
+          <t>https://artportalen.se/Sighting/118763764</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118769848</v>
+        <v>118766285</v>
       </c>
       <c r="B6" t="n">
         <v>80433</v>
@@ -1119,17 +1119,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475286</v>
+        <v>475155</v>
       </c>
       <c r="R6" t="n">
-        <v>6853351</v>
+        <v>6853357</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,13 +1184,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769848</t>
+          <t>https://artportalen.se/Sighting/118766285</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118769849</v>
+        <v>118766652</v>
       </c>
       <c r="B7" t="n">
         <v>80433</v>
@@ -1221,17 +1221,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475179</v>
+        <v>475065</v>
       </c>
       <c r="R7" t="n">
-        <v>6853119</v>
+        <v>6853275</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1286,38 +1286,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769849</t>
+          <t>https://artportalen.se/Sighting/118766652</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118769844</v>
+        <v>118769848</v>
       </c>
       <c r="B8" t="n">
-        <v>91872</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474897</v>
+        <v>475286</v>
       </c>
       <c r="R8" t="n">
-        <v>6852835</v>
+        <v>6853351</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1388,38 +1388,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769844</t>
+          <t>https://artportalen.se/Sighting/118769848</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118769874</v>
+        <v>118769849</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475265</v>
+        <v>475179</v>
       </c>
       <c r="R9" t="n">
-        <v>6853105</v>
+        <v>6853119</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1490,54 +1490,54 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769874</t>
+          <t>https://artportalen.se/Sighting/118769849</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118762886</v>
+        <v>118769844</v>
       </c>
       <c r="B10" t="n">
-        <v>80432</v>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474862</v>
+        <v>474897</v>
       </c>
       <c r="R10" t="n">
-        <v>6852981</v>
+        <v>6852835</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,65 +1581,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118762886</t>
+          <t>https://artportalen.se/Sighting/118769844</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118763114</v>
+        <v>118769874</v>
       </c>
       <c r="B11" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474930</v>
+        <v>475265</v>
       </c>
       <c r="R11" t="n">
-        <v>6853098</v>
+        <v>6853105</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1683,49 +1683,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118763114</t>
+          <t>https://artportalen.se/Sighting/118769874</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118763770</v>
+        <v>135600514</v>
       </c>
       <c r="B12" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475208</v>
+        <v>474926</v>
       </c>
       <c r="R12" t="n">
-        <v>6853108</v>
+        <v>6853016</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,13 +1796,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118763770</t>
+          <t>https://artportalen.se/Sighting/135600514</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118765456</v>
+        <v>118762886</v>
       </c>
       <c r="B13" t="n">
         <v>80432</v>
@@ -1833,17 +1833,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475349</v>
+        <v>474862</v>
       </c>
       <c r="R13" t="n">
-        <v>6853384</v>
+        <v>6852981</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1887,24 +1887,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118765456</t>
+          <t>https://artportalen.se/Sighting/118762886</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118765546</v>
+        <v>118763114</v>
       </c>
       <c r="B14" t="n">
         <v>80432</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475240</v>
+        <v>474930</v>
       </c>
       <c r="R14" t="n">
-        <v>6853164</v>
+        <v>6853098</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2000,13 +2000,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118765546</t>
+          <t>https://artportalen.se/Sighting/118763114</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118766297</v>
+        <v>118763770</v>
       </c>
       <c r="B15" t="n">
         <v>80432</v>
@@ -2037,17 +2037,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475153</v>
+        <v>475208</v>
       </c>
       <c r="R15" t="n">
-        <v>6853357</v>
+        <v>6853108</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2091,24 +2091,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766297</t>
+          <t>https://artportalen.se/Sighting/118763770</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118766672</v>
+        <v>118765456</v>
       </c>
       <c r="B16" t="n">
         <v>80432</v>
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475054</v>
+        <v>475349</v>
       </c>
       <c r="R16" t="n">
-        <v>6853284</v>
+        <v>6853384</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2204,13 +2204,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766672</t>
+          <t>https://artportalen.se/Sighting/118765456</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118769852</v>
+        <v>118765546</v>
       </c>
       <c r="B17" t="n">
         <v>80432</v>
@@ -2241,14 +2241,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475281</v>
+        <v>475240</v>
       </c>
       <c r="R17" t="n">
-        <v>6853211</v>
+        <v>6853164</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2295,24 +2295,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769852</t>
+          <t>https://artportalen.se/Sighting/118765546</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118769853</v>
+        <v>118766297</v>
       </c>
       <c r="B18" t="n">
         <v>80432</v>
@@ -2343,17 +2343,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475286</v>
+        <v>475153</v>
       </c>
       <c r="R18" t="n">
-        <v>6853198</v>
+        <v>6853357</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2408,13 +2408,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769853</t>
+          <t>https://artportalen.se/Sighting/118766297</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118769855</v>
+        <v>118766672</v>
       </c>
       <c r="B19" t="n">
         <v>80432</v>
@@ -2445,17 +2445,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475284</v>
+        <v>475054</v>
       </c>
       <c r="R19" t="n">
-        <v>6853186</v>
+        <v>6853284</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2510,13 +2510,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769855</t>
+          <t>https://artportalen.se/Sighting/118766672</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118769856</v>
+        <v>118769852</v>
       </c>
       <c r="B20" t="n">
         <v>80432</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475300</v>
+        <v>475281</v>
       </c>
       <c r="R20" t="n">
-        <v>6853182</v>
+        <v>6853211</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2612,54 +2612,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769856</t>
+          <t>https://artportalen.se/Sighting/118769852</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118766686</v>
+        <v>118769853</v>
       </c>
       <c r="B21" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475054</v>
+        <v>475286</v>
       </c>
       <c r="R21" t="n">
-        <v>6853272</v>
+        <v>6853198</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2714,38 +2714,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766686</t>
+          <t>https://artportalen.se/Sighting/118769853</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118769846</v>
+        <v>118769855</v>
       </c>
       <c r="B22" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474860</v>
+        <v>475284</v>
       </c>
       <c r="R22" t="n">
-        <v>6852995</v>
+        <v>6853186</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2816,38 +2816,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769846</t>
+          <t>https://artportalen.se/Sighting/118769855</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118769876</v>
+        <v>118769856</v>
       </c>
       <c r="B23" t="n">
-        <v>80467</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475176</v>
+        <v>475300</v>
       </c>
       <c r="R23" t="n">
-        <v>6853122</v>
+        <v>6853182</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2918,16 +2918,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769876</t>
+          <t>https://artportalen.se/Sighting/118769856</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118770271</v>
+        <v>135601049</v>
       </c>
       <c r="B24" t="n">
-        <v>58114</v>
+        <v>80488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2935,45 +2935,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475175</v>
+        <v>474908</v>
       </c>
       <c r="R24" t="n">
-        <v>6853143</v>
+        <v>6853087</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2997,12 +2989,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3017,27 +3009,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118770271</t>
+          <t>https://artportalen.se/Sighting/135601049</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118769873</v>
+        <v>118766686</v>
       </c>
       <c r="B25" t="n">
-        <v>56905</v>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,37 +3037,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208260</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474840</v>
+        <v>475054</v>
       </c>
       <c r="R25" t="n">
-        <v>6852984</v>
+        <v>6853272</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3130,16 +3122,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769873</t>
+          <t>https://artportalen.se/Sighting/118766686</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118766502</v>
+        <v>118769846</v>
       </c>
       <c r="B26" t="n">
-        <v>99022</v>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,37 +3139,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220093</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475093</v>
+        <v>474860</v>
       </c>
       <c r="R26" t="n">
-        <v>6853257</v>
+        <v>6852995</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3221,27 +3213,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766502</t>
+          <t>https://artportalen.se/Sighting/118769846</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118769859</v>
+        <v>118769876</v>
       </c>
       <c r="B27" t="n">
-        <v>99022</v>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3249,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220093</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3273,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>475091</v>
+        <v>475176</v>
       </c>
       <c r="R27" t="n">
-        <v>6853271</v>
+        <v>6853122</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3334,54 +3326,62 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769859</t>
+          <t>https://artportalen.se/Sighting/118769876</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118762153</v>
+        <v>118770271</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474905</v>
+        <v>475175</v>
       </c>
       <c r="R28" t="n">
-        <v>6852851</v>
+        <v>6853143</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3425,49 +3425,49 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118762153</t>
+          <t>https://artportalen.se/Sighting/118770271</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118762480</v>
+        <v>135597601</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>58136</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474949</v>
+        <v>474896</v>
       </c>
       <c r="R29" t="n">
-        <v>6852843</v>
+        <v>6852956</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3507,12 +3507,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3538,54 +3538,54 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118762480</t>
+          <t>https://artportalen.se/Sighting/135597601</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118762626</v>
+        <v>118769873</v>
       </c>
       <c r="B30" t="n">
-        <v>99118</v>
+        <v>56905</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>208260</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474988</v>
+        <v>474840</v>
       </c>
       <c r="R30" t="n">
-        <v>6852930</v>
+        <v>6852984</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3629,71 +3629,62 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118762626</t>
+          <t>https://artportalen.se/Sighting/118769873</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118762755</v>
+        <v>118766502</v>
       </c>
       <c r="B31" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475026</v>
+        <v>475093</v>
       </c>
       <c r="R31" t="n">
-        <v>6852933</v>
+        <v>6853257</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3751,54 +3742,54 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118762755</t>
+          <t>https://artportalen.se/Sighting/118766502</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118763353</v>
+        <v>118769859</v>
       </c>
       <c r="B32" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475052</v>
+        <v>475091</v>
       </c>
       <c r="R32" t="n">
-        <v>6853129</v>
+        <v>6853271</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3842,24 +3833,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118763353</t>
+          <t>https://artportalen.se/Sighting/118769859</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118763600</v>
+        <v>118762153</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -3894,10 +3885,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>475143</v>
+        <v>474905</v>
       </c>
       <c r="R33" t="n">
-        <v>6853105</v>
+        <v>6852851</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3955,13 +3946,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118763600</t>
+          <t>https://artportalen.se/Sighting/118762153</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118763943</v>
+        <v>118762480</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -3996,13 +3987,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475284</v>
+        <v>474949</v>
       </c>
       <c r="R34" t="n">
-        <v>6853102</v>
+        <v>6852843</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4057,13 +4048,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118763943</t>
+          <t>https://artportalen.se/Sighting/118762480</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118764888</v>
+        <v>118762626</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4098,13 +4089,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475321</v>
+        <v>474988</v>
       </c>
       <c r="R35" t="n">
-        <v>6853346</v>
+        <v>6852930</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4159,13 +4150,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118764888</t>
+          <t>https://artportalen.se/Sighting/118762626</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118765071</v>
+        <v>118762755</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4193,20 +4184,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475339</v>
+        <v>475026</v>
       </c>
       <c r="R36" t="n">
-        <v>6853351</v>
+        <v>6852933</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4261,13 +4261,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118765071</t>
+          <t>https://artportalen.se/Sighting/118762755</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118765086</v>
+        <v>118763353</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4298,17 +4298,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475303</v>
+        <v>475052</v>
       </c>
       <c r="R37" t="n">
-        <v>6853364</v>
+        <v>6853129</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4352,24 +4352,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118765086</t>
+          <t>https://artportalen.se/Sighting/118763353</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118765092</v>
+        <v>118763600</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -4404,13 +4404,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475341</v>
+        <v>475143</v>
       </c>
       <c r="R38" t="n">
-        <v>6853346</v>
+        <v>6853105</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4465,13 +4465,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118765092</t>
+          <t>https://artportalen.se/Sighting/118763600</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118765116</v>
+        <v>118763943</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -4502,17 +4502,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475300</v>
+        <v>475284</v>
       </c>
       <c r="R39" t="n">
-        <v>6853368</v>
+        <v>6853102</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4556,24 +4556,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118765116</t>
+          <t>https://artportalen.se/Sighting/118763943</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118765189</v>
+        <v>118764888</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -4608,10 +4608,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475342</v>
+        <v>475321</v>
       </c>
       <c r="R40" t="n">
-        <v>6853462</v>
+        <v>6853346</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4669,13 +4669,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118765189</t>
+          <t>https://artportalen.se/Sighting/118764888</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118765796</v>
+        <v>118765071</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -4706,14 +4706,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475325</v>
+        <v>475339</v>
       </c>
       <c r="R41" t="n">
-        <v>6853434</v>
+        <v>6853351</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4760,24 +4760,24 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118765796</t>
+          <t>https://artportalen.se/Sighting/118765071</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118766005</v>
+        <v>118765086</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475286</v>
+        <v>475303</v>
       </c>
       <c r="R42" t="n">
-        <v>6853383</v>
+        <v>6853364</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4873,13 +4873,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766005</t>
+          <t>https://artportalen.se/Sighting/118765086</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118766023</v>
+        <v>118765092</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -4910,17 +4910,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475261</v>
+        <v>475341</v>
       </c>
       <c r="R43" t="n">
-        <v>6853378</v>
+        <v>6853346</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4964,24 +4964,24 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766023</t>
+          <t>https://artportalen.se/Sighting/118765092</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118766078</v>
+        <v>118765116</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -5012,17 +5012,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475291</v>
+        <v>475300</v>
       </c>
       <c r="R44" t="n">
-        <v>6853381</v>
+        <v>6853368</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5052,11 +5052,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>15-tal individer</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5071,24 +5066,24 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766078</t>
+          <t>https://artportalen.se/Sighting/118765116</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118766126</v>
+        <v>118765189</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -5119,17 +5114,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475221</v>
+        <v>475342</v>
       </c>
       <c r="R45" t="n">
-        <v>6853376</v>
+        <v>6853462</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5173,24 +5168,24 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766126</t>
+          <t>https://artportalen.se/Sighting/118765189</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118766193</v>
+        <v>118765796</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -5221,17 +5216,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475229</v>
+        <v>475325</v>
       </c>
       <c r="R46" t="n">
-        <v>6853392</v>
+        <v>6853434</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5275,24 +5270,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766193</t>
+          <t>https://artportalen.se/Sighting/118765796</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118766206</v>
+        <v>118766005</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -5327,13 +5322,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475201</v>
+        <v>475286</v>
       </c>
       <c r="R47" t="n">
-        <v>6853392</v>
+        <v>6853383</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5363,11 +5358,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5393,13 +5383,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766206</t>
+          <t>https://artportalen.se/Sighting/118766005</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118766233</v>
+        <v>118766023</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -5434,13 +5424,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475181</v>
+        <v>475261</v>
       </c>
       <c r="R48" t="n">
-        <v>6853364</v>
+        <v>6853378</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5495,13 +5485,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766233</t>
+          <t>https://artportalen.se/Sighting/118766023</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118766302</v>
+        <v>118766078</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -5529,26 +5519,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475179</v>
+        <v>475291</v>
       </c>
       <c r="R49" t="n">
-        <v>6853360</v>
+        <v>6853381</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5583,6 +5564,11 @@
           <t>2024-07-29</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>15-tal individer</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5606,13 +5592,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766302</t>
+          <t>https://artportalen.se/Sighting/118766078</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118766365</v>
+        <v>118766126</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -5647,10 +5633,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475137</v>
+        <v>475221</v>
       </c>
       <c r="R50" t="n">
-        <v>6853331</v>
+        <v>6853376</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5708,13 +5694,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766365</t>
+          <t>https://artportalen.se/Sighting/118766126</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118766370</v>
+        <v>118766193</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -5749,13 +5735,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475119</v>
+        <v>475229</v>
       </c>
       <c r="R51" t="n">
-        <v>6853325</v>
+        <v>6853392</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5810,13 +5796,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766370</t>
+          <t>https://artportalen.se/Sighting/118766193</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118766394</v>
+        <v>118766206</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -5851,10 +5837,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475130</v>
+        <v>475201</v>
       </c>
       <c r="R52" t="n">
-        <v>6853328</v>
+        <v>6853392</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5889,6 +5875,11 @@
           <t>2024-07-29</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5912,13 +5903,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766394</t>
+          <t>https://artportalen.se/Sighting/118766206</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118766412</v>
+        <v>118766233</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -5953,13 +5944,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>475111</v>
+        <v>475181</v>
       </c>
       <c r="R53" t="n">
-        <v>6853306</v>
+        <v>6853364</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6014,13 +6005,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766412</t>
+          <t>https://artportalen.se/Sighting/118766233</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118766545</v>
+        <v>118766302</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6048,17 +6039,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>475103</v>
+        <v>475179</v>
       </c>
       <c r="R54" t="n">
-        <v>6853253</v>
+        <v>6853360</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6116,13 +6116,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766545</t>
+          <t>https://artportalen.se/Sighting/118766302</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118766589</v>
+        <v>118766365</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -6153,17 +6153,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475060</v>
+        <v>475137</v>
       </c>
       <c r="R55" t="n">
-        <v>6853289</v>
+        <v>6853331</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6207,24 +6207,24 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766589</t>
+          <t>https://artportalen.se/Sighting/118766365</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118766595</v>
+        <v>118766370</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -6255,17 +6255,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475079</v>
+        <v>475119</v>
       </c>
       <c r="R56" t="n">
-        <v>6853256</v>
+        <v>6853325</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6309,24 +6309,24 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118766595</t>
+          <t>https://artportalen.se/Sighting/118766370</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118769860</v>
+        <v>118766394</v>
       </c>
       <c r="B57" t="n">
         <v>99118</v>
@@ -6357,17 +6357,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>475001</v>
+        <v>475130</v>
       </c>
       <c r="R57" t="n">
-        <v>6852915</v>
+        <v>6853328</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6397,11 +6397,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6427,13 +6422,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769860</t>
+          <t>https://artportalen.se/Sighting/118766394</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118769861</v>
+        <v>118766412</v>
       </c>
       <c r="B58" t="n">
         <v>99118</v>
@@ -6464,17 +6459,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>475079</v>
+        <v>475111</v>
       </c>
       <c r="R58" t="n">
-        <v>6853115</v>
+        <v>6853306</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6504,11 +6499,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6534,13 +6524,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769861</t>
+          <t>https://artportalen.se/Sighting/118766412</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118769862</v>
+        <v>118766545</v>
       </c>
       <c r="B59" t="n">
         <v>99118</v>
@@ -6571,17 +6561,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>475095</v>
+        <v>475103</v>
       </c>
       <c r="R59" t="n">
-        <v>6853273</v>
+        <v>6853253</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6625,24 +6615,24 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769862</t>
+          <t>https://artportalen.se/Sighting/118766545</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118769863</v>
+        <v>118766589</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -6673,17 +6663,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>475302</v>
+        <v>475060</v>
       </c>
       <c r="R60" t="n">
-        <v>6853363</v>
+        <v>6853289</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6727,24 +6717,24 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769863</t>
+          <t>https://artportalen.se/Sighting/118766589</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118769865</v>
+        <v>118766595</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -6775,17 +6765,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fågelsjö, Hjd</t>
+          <t>Sjöarbergsvallen, Sjöarbergsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>475295</v>
+        <v>475079</v>
       </c>
       <c r="R61" t="n">
-        <v>6853180</v>
+        <v>6853256</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6840,13 +6830,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769865</t>
+          <t>https://artportalen.se/Sighting/118766595</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118769866</v>
+        <v>118769860</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -6881,10 +6871,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>475289</v>
+        <v>475001</v>
       </c>
       <c r="R62" t="n">
-        <v>6853167</v>
+        <v>6852915</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6919,6 +6909,11 @@
           <t>2024-07-29</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6942,13 +6937,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769866</t>
+          <t>https://artportalen.se/Sighting/118769860</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118769867</v>
+        <v>118769861</v>
       </c>
       <c r="B63" t="n">
         <v>99118</v>
@@ -6983,10 +6978,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>475281</v>
+        <v>475079</v>
       </c>
       <c r="R63" t="n">
-        <v>6853098</v>
+        <v>6853115</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7021,6 +7016,11 @@
           <t>2024-07-29</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7044,13 +7044,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769867</t>
+          <t>https://artportalen.se/Sighting/118769861</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118769869</v>
+        <v>118769862</v>
       </c>
       <c r="B64" t="n">
         <v>99118</v>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>474841</v>
+        <v>475095</v>
       </c>
       <c r="R64" t="n">
-        <v>6852986</v>
+        <v>6853273</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7146,13 +7146,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769869</t>
+          <t>https://artportalen.se/Sighting/118769862</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118769870</v>
+        <v>118769863</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -7187,10 +7187,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>474936</v>
+        <v>475302</v>
       </c>
       <c r="R65" t="n">
-        <v>6852846</v>
+        <v>6853363</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7248,13 +7248,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769870</t>
+          <t>https://artportalen.se/Sighting/118769863</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118769871</v>
+        <v>118769865</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>475275</v>
+        <v>475295</v>
       </c>
       <c r="R66" t="n">
-        <v>6853238</v>
+        <v>6853180</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7350,38 +7350,38 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769871</t>
+          <t>https://artportalen.se/Sighting/118769865</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118769847</v>
+        <v>118769866</v>
       </c>
       <c r="B67" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7391,10 +7391,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>474904</v>
+        <v>475289</v>
       </c>
       <c r="R67" t="n">
-        <v>6852836</v>
+        <v>6853167</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7452,54 +7452,54 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118769847</t>
+          <t>https://artportalen.se/Sighting/118769866</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118763737</v>
+        <v>118769867</v>
       </c>
       <c r="B68" t="n">
-        <v>80392</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+          <t>Fågelsjö, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>475209</v>
+        <v>475281</v>
       </c>
       <c r="R68" t="n">
-        <v>6853105</v>
+        <v>6853098</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7543,16 +7543,4945 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769867</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>118769869</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>474841</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6852986</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769869</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>118769870</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>474936</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6852846</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769870</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>118769871</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>475275</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6853238</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769871</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135597460</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>474891</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6852929</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135597460</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135597656</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>474900</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6852961</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135597656</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135597873</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>474908</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6852965</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135597873</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135597960</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>474899</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6852967</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135597960</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135598014</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>474898</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6852994</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135598014</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135598068</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>474900</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6852995</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135598068</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135598373</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>474833</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6853040</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135598373</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135598420</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>474832</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6853044</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135598420</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135598509</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>474829</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6853027</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135598509</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135598562</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>474830</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6853024</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135598562</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135598590</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>474832</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6853019</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135598590</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135598647</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>474838</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6853008</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135598647</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135598703</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>474834</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6852988</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135598703</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>135598769</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>474831</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6852982</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135598769</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135598854</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>474834</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6852972</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135598854</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135598878</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>474841</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6852969</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135598878</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135598959</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>474845</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6852948</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135598959</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135598992</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>474842</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6852960</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135598992</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135599030</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>474853</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6852958</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135599030</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135599166</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>474865</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6852945</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135599166</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135599188</v>
+      </c>
+      <c r="B92" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>474871</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6852952</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135599188</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135599231</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>474865</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6852960</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135599231</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135599262</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>474870</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6852964</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135599262</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135599343</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>474868</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6852978</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135599343</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>135599579</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>474850</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6852993</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135599579</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>135599640</v>
+      </c>
+      <c r="B97" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>474816</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6853002</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135599640</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>135599693</v>
+      </c>
+      <c r="B98" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>474817</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6853009</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135599693</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>135600266</v>
+      </c>
+      <c r="B99" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>474896</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6853009</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135600266</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>135600329</v>
+      </c>
+      <c r="B100" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>474916</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6853000</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135600329</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>135600739</v>
+      </c>
+      <c r="B101" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>474956</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6853070</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135600739</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>135600767</v>
+      </c>
+      <c r="B102" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>474950</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6853081</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135600767</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>135600810</v>
+      </c>
+      <c r="B103" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>474934</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6853089</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135600810</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>135600822</v>
+      </c>
+      <c r="B104" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>474936</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6853094</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135600822</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>135600944</v>
+      </c>
+      <c r="B105" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>474924</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6853106</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135600944</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>135601170</v>
+      </c>
+      <c r="B106" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>474894</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6853063</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135601170</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>135601231</v>
+      </c>
+      <c r="B107" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>474892</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6853071</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135601231</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>135601270</v>
+      </c>
+      <c r="B108" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>474875</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6853070</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135601270</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>135601309</v>
+      </c>
+      <c r="B109" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>474869</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6853065</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135601309</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>135601357</v>
+      </c>
+      <c r="B110" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>474864</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6853067</v>
+      </c>
+      <c r="S110" t="n">
+        <v>5</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135601357</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>135601440</v>
+      </c>
+      <c r="B111" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>474865</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6853056</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135601440</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>135601472</v>
+      </c>
+      <c r="B112" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>474859</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6853050</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135601472</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>135601508</v>
+      </c>
+      <c r="B113" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>474860</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6853044</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135601508</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>118769847</v>
+      </c>
+      <c r="B114" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>474904</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6852836</v>
+      </c>
+      <c r="S114" t="n">
+        <v>25</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118769847</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>118763737</v>
+      </c>
+      <c r="B115" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Hälltjärnen, Hälltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>475209</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6853105</v>
+      </c>
+      <c r="S115" t="n">
+        <v>20</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/118763737</t>
         </is>
@@ -7627,6 +12556,53 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135601119</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135657014</v>
       </c>
       <c r="B4" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135600489</v>
       </c>
       <c r="B5" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135657035</v>
       </c>
       <c r="B6" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135657036</v>
       </c>
       <c r="B7" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135657038</v>
       </c>
       <c r="B8" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>135600514</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135657013</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>135657015</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>135657000</v>
       </c>
       <c r="B30" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>135656980</v>
       </c>
       <c r="B31" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>135657022</v>
       </c>
       <c r="B32" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>135657043</v>
       </c>
       <c r="B39" t="n">
-        <v>99277</v>
+        <v>99304</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>135597460</v>
       </c>
       <c r="B81" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>135597656</v>
       </c>
       <c r="B82" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>135597873</v>
       </c>
       <c r="B83" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135597960</v>
       </c>
       <c r="B84" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>135598014</v>
       </c>
       <c r="B85" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>135598068</v>
       </c>
       <c r="B86" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>135598373</v>
       </c>
       <c r="B87" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>135598420</v>
       </c>
       <c r="B88" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>135598509</v>
       </c>
       <c r="B89" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>135598562</v>
       </c>
       <c r="B90" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>135598590</v>
       </c>
       <c r="B91" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>135598647</v>
       </c>
       <c r="B92" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>135598703</v>
       </c>
       <c r="B93" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>135598769</v>
       </c>
       <c r="B94" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>135598854</v>
       </c>
       <c r="B95" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>135598878</v>
       </c>
       <c r="B96" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>135598959</v>
       </c>
       <c r="B97" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>135598992</v>
       </c>
       <c r="B98" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>135599030</v>
       </c>
       <c r="B99" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>135599166</v>
       </c>
       <c r="B100" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>135599188</v>
       </c>
       <c r="B101" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135599231</v>
       </c>
       <c r="B102" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>135599262</v>
       </c>
       <c r="B103" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>135599343</v>
       </c>
       <c r="B104" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>135599579</v>
       </c>
       <c r="B105" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>135599640</v>
       </c>
       <c r="B106" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>135599693</v>
       </c>
       <c r="B107" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>135600266</v>
       </c>
       <c r="B108" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>135600329</v>
       </c>
       <c r="B109" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>135600739</v>
       </c>
       <c r="B110" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>135600767</v>
       </c>
       <c r="B111" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>135600810</v>
       </c>
       <c r="B112" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>135600822</v>
       </c>
       <c r="B113" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>135600944</v>
       </c>
       <c r="B114" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>135601170</v>
       </c>
       <c r="B115" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>135601231</v>
       </c>
       <c r="B116" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>135601270</v>
       </c>
       <c r="B117" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>135601309</v>
       </c>
       <c r="B118" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>135601357</v>
       </c>
       <c r="B119" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>135601440</v>
       </c>
       <c r="B120" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>135601472</v>
       </c>
       <c r="B121" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>135601508</v>
       </c>
       <c r="B122" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>135656952</v>
       </c>
       <c r="B123" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>135656953</v>
       </c>
       <c r="B124" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>135656955</v>
       </c>
       <c r="B125" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>135656957</v>
       </c>
       <c r="B126" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>135656958</v>
       </c>
       <c r="B127" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>135656959</v>
       </c>
       <c r="B128" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>135656960</v>
       </c>
       <c r="B129" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>135656961</v>
       </c>
       <c r="B130" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>135656962</v>
       </c>
       <c r="B131" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>135656963</v>
       </c>
       <c r="B132" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>135656964</v>
       </c>
       <c r="B133" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>135656965</v>
       </c>
       <c r="B134" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>135656966</v>
       </c>
       <c r="B135" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>135656967</v>
       </c>
       <c r="B136" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>135656968</v>
       </c>
       <c r="B137" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>135656969</v>
       </c>
       <c r="B138" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>135656970</v>
       </c>
       <c r="B139" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>135656971</v>
       </c>
       <c r="B140" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>135656972</v>
       </c>
       <c r="B141" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>135656973</v>
       </c>
       <c r="B142" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135656974</v>
       </c>
       <c r="B143" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>135656975</v>
       </c>
       <c r="B144" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>135656976</v>
       </c>
       <c r="B145" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>135656977</v>
       </c>
       <c r="B146" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>135656978</v>
       </c>
       <c r="B147" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>135656979</v>
       </c>
       <c r="B148" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>135656981</v>
       </c>
       <c r="B149" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>135656982</v>
       </c>
       <c r="B150" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>135656987</v>
       </c>
       <c r="B151" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>135656989</v>
       </c>
       <c r="B152" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>135656992</v>
       </c>
       <c r="B153" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>135656993</v>
       </c>
       <c r="B154" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>135656997</v>
       </c>
       <c r="B155" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>135656998</v>
       </c>
       <c r="B156" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>135656999</v>
       </c>
       <c r="B157" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>135657001</v>
       </c>
       <c r="B158" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>135657002</v>
       </c>
       <c r="B159" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>135657003</v>
       </c>
       <c r="B160" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>135657004</v>
       </c>
       <c r="B161" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>135657005</v>
       </c>
       <c r="B162" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>135657006</v>
       </c>
       <c r="B163" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>135657007</v>
       </c>
       <c r="B164" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>135657008</v>
       </c>
       <c r="B165" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>135657010</v>
       </c>
       <c r="B166" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>135657011</v>
       </c>
       <c r="B167" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>135657016</v>
       </c>
       <c r="B168" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>135657017</v>
       </c>
       <c r="B169" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>135657018</v>
       </c>
       <c r="B170" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>135657019</v>
       </c>
       <c r="B171" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>135657020</v>
       </c>
       <c r="B172" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>135657023</v>
       </c>
       <c r="B173" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>135657024</v>
       </c>
       <c r="B174" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>135657025</v>
       </c>
       <c r="B175" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>135657029</v>
       </c>
       <c r="B176" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>135657030</v>
       </c>
       <c r="B177" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>135657032</v>
       </c>
       <c r="B178" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>135657033</v>
       </c>
       <c r="B179" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>135657034</v>
       </c>
       <c r="B180" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>135657039</v>
       </c>
       <c r="B181" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>135657040</v>
       </c>
       <c r="B182" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>135657041</v>
       </c>
       <c r="B183" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>135657042</v>
       </c>
       <c r="B184" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>135657044</v>
       </c>
       <c r="B185" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>135657045</v>
       </c>
       <c r="B186" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>135657014</v>
       </c>
       <c r="B4" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135600489</v>
       </c>
       <c r="B5" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135657035</v>
       </c>
       <c r="B6" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135657036</v>
       </c>
       <c r="B7" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135657038</v>
       </c>
       <c r="B8" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>135657043</v>
       </c>
       <c r="B39" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>135597460</v>
       </c>
       <c r="B81" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>135597656</v>
       </c>
       <c r="B82" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>135597873</v>
       </c>
       <c r="B83" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135597960</v>
       </c>
       <c r="B84" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>135598014</v>
       </c>
       <c r="B85" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>135598068</v>
       </c>
       <c r="B86" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>135598373</v>
       </c>
       <c r="B87" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>135598420</v>
       </c>
       <c r="B88" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>135598509</v>
       </c>
       <c r="B89" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>135598562</v>
       </c>
       <c r="B90" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>135598590</v>
       </c>
       <c r="B91" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>135598647</v>
       </c>
       <c r="B92" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>135598703</v>
       </c>
       <c r="B93" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>135598769</v>
       </c>
       <c r="B94" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>135598854</v>
       </c>
       <c r="B95" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>135598878</v>
       </c>
       <c r="B96" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>135598959</v>
       </c>
       <c r="B97" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>135598992</v>
       </c>
       <c r="B98" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>135599030</v>
       </c>
       <c r="B99" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>135599166</v>
       </c>
       <c r="B100" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>135599188</v>
       </c>
       <c r="B101" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135599231</v>
       </c>
       <c r="B102" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>135599262</v>
       </c>
       <c r="B103" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>135599343</v>
       </c>
       <c r="B104" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>135599579</v>
       </c>
       <c r="B105" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>135599640</v>
       </c>
       <c r="B106" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>135599693</v>
       </c>
       <c r="B107" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>135600266</v>
       </c>
       <c r="B108" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>135600329</v>
       </c>
       <c r="B109" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>135600739</v>
       </c>
       <c r="B110" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>135600767</v>
       </c>
       <c r="B111" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>135600810</v>
       </c>
       <c r="B112" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>135600822</v>
       </c>
       <c r="B113" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>135600944</v>
       </c>
       <c r="B114" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>135601170</v>
       </c>
       <c r="B115" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>135601231</v>
       </c>
       <c r="B116" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>135601270</v>
       </c>
       <c r="B117" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>135601309</v>
       </c>
       <c r="B118" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>135601357</v>
       </c>
       <c r="B119" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>135601440</v>
       </c>
       <c r="B120" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>135601472</v>
       </c>
       <c r="B121" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>135601508</v>
       </c>
       <c r="B122" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>135656952</v>
       </c>
       <c r="B123" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>135656953</v>
       </c>
       <c r="B124" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>135656955</v>
       </c>
       <c r="B125" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>135656957</v>
       </c>
       <c r="B126" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>135656958</v>
       </c>
       <c r="B127" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>135656959</v>
       </c>
       <c r="B128" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>135656960</v>
       </c>
       <c r="B129" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>135656961</v>
       </c>
       <c r="B130" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>135656962</v>
       </c>
       <c r="B131" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>135656963</v>
       </c>
       <c r="B132" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>135656964</v>
       </c>
       <c r="B133" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>135656965</v>
       </c>
       <c r="B134" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>135656966</v>
       </c>
       <c r="B135" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>135656967</v>
       </c>
       <c r="B136" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>135656968</v>
       </c>
       <c r="B137" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>135656969</v>
       </c>
       <c r="B138" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>135656970</v>
       </c>
       <c r="B139" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>135656971</v>
       </c>
       <c r="B140" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>135656972</v>
       </c>
       <c r="B141" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>135656973</v>
       </c>
       <c r="B142" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135656974</v>
       </c>
       <c r="B143" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>135656975</v>
       </c>
       <c r="B144" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>135656976</v>
       </c>
       <c r="B145" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>135656977</v>
       </c>
       <c r="B146" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>135656978</v>
       </c>
       <c r="B147" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>135656979</v>
       </c>
       <c r="B148" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>135656981</v>
       </c>
       <c r="B149" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>135656982</v>
       </c>
       <c r="B150" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>135656987</v>
       </c>
       <c r="B151" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>135656989</v>
       </c>
       <c r="B152" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>135656992</v>
       </c>
       <c r="B153" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>135656993</v>
       </c>
       <c r="B154" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>135656997</v>
       </c>
       <c r="B155" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>135656998</v>
       </c>
       <c r="B156" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>135656999</v>
       </c>
       <c r="B157" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>135657001</v>
       </c>
       <c r="B158" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>135657002</v>
       </c>
       <c r="B159" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>135657003</v>
       </c>
       <c r="B160" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>135657004</v>
       </c>
       <c r="B161" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>135657005</v>
       </c>
       <c r="B162" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>135657006</v>
       </c>
       <c r="B163" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>135657007</v>
       </c>
       <c r="B164" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>135657008</v>
       </c>
       <c r="B165" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>135657010</v>
       </c>
       <c r="B166" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>135657011</v>
       </c>
       <c r="B167" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>135657016</v>
       </c>
       <c r="B168" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>135657017</v>
       </c>
       <c r="B169" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>135657018</v>
       </c>
       <c r="B170" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>135657019</v>
       </c>
       <c r="B171" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>135657020</v>
       </c>
       <c r="B172" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>135657023</v>
       </c>
       <c r="B173" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>135657024</v>
       </c>
       <c r="B174" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>135657025</v>
       </c>
       <c r="B175" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>135657029</v>
       </c>
       <c r="B176" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>135657030</v>
       </c>
       <c r="B177" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>135657032</v>
       </c>
       <c r="B178" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>135657033</v>
       </c>
       <c r="B179" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>135657034</v>
       </c>
       <c r="B180" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>135657039</v>
       </c>
       <c r="B181" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>135657040</v>
       </c>
       <c r="B182" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>135657041</v>
       </c>
       <c r="B183" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>135657042</v>
       </c>
       <c r="B184" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>135657044</v>
       </c>
       <c r="B185" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>135657045</v>
       </c>
       <c r="B186" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135601119</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135657014</v>
       </c>
       <c r="B4" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135600489</v>
       </c>
       <c r="B5" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135657035</v>
       </c>
       <c r="B6" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135657036</v>
       </c>
       <c r="B7" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135657038</v>
       </c>
       <c r="B8" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>135600514</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135657013</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>135657015</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>135657000</v>
       </c>
       <c r="B30" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>135656980</v>
       </c>
       <c r="B31" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>135657022</v>
       </c>
       <c r="B32" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>135597601</v>
       </c>
       <c r="B37" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>135657043</v>
       </c>
       <c r="B39" t="n">
-        <v>99311</v>
+        <v>99328</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>135597460</v>
       </c>
       <c r="B81" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>135597656</v>
       </c>
       <c r="B82" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>135597873</v>
       </c>
       <c r="B83" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135597960</v>
       </c>
       <c r="B84" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>135598014</v>
       </c>
       <c r="B85" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>135598068</v>
       </c>
       <c r="B86" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>135598373</v>
       </c>
       <c r="B87" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>135598420</v>
       </c>
       <c r="B88" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>135598509</v>
       </c>
       <c r="B89" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>135598562</v>
       </c>
       <c r="B90" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>135598590</v>
       </c>
       <c r="B91" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>135598647</v>
       </c>
       <c r="B92" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>135598703</v>
       </c>
       <c r="B93" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>135598769</v>
       </c>
       <c r="B94" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>135598854</v>
       </c>
       <c r="B95" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>135598878</v>
       </c>
       <c r="B96" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>135598959</v>
       </c>
       <c r="B97" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>135598992</v>
       </c>
       <c r="B98" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>135599030</v>
       </c>
       <c r="B99" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>135599166</v>
       </c>
       <c r="B100" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>135599188</v>
       </c>
       <c r="B101" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135599231</v>
       </c>
       <c r="B102" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>135599262</v>
       </c>
       <c r="B103" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>135599343</v>
       </c>
       <c r="B104" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>135599579</v>
       </c>
       <c r="B105" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>135599640</v>
       </c>
       <c r="B106" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>135599693</v>
       </c>
       <c r="B107" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>135600266</v>
       </c>
       <c r="B108" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>135600329</v>
       </c>
       <c r="B109" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>135600739</v>
       </c>
       <c r="B110" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>135600767</v>
       </c>
       <c r="B111" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>135600810</v>
       </c>
       <c r="B112" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>135600822</v>
       </c>
       <c r="B113" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>135600944</v>
       </c>
       <c r="B114" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>135601170</v>
       </c>
       <c r="B115" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>135601231</v>
       </c>
       <c r="B116" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>135601270</v>
       </c>
       <c r="B117" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>135601309</v>
       </c>
       <c r="B118" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>135601357</v>
       </c>
       <c r="B119" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>135601440</v>
       </c>
       <c r="B120" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>135601472</v>
       </c>
       <c r="B121" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>135601508</v>
       </c>
       <c r="B122" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>135656952</v>
       </c>
       <c r="B123" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>135656953</v>
       </c>
       <c r="B124" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>135656955</v>
       </c>
       <c r="B125" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>135656957</v>
       </c>
       <c r="B126" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>135656958</v>
       </c>
       <c r="B127" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>135656959</v>
       </c>
       <c r="B128" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>135656960</v>
       </c>
       <c r="B129" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>135656961</v>
       </c>
       <c r="B130" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>135656962</v>
       </c>
       <c r="B131" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>135656963</v>
       </c>
       <c r="B132" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>135656964</v>
       </c>
       <c r="B133" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>135656965</v>
       </c>
       <c r="B134" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>135656966</v>
       </c>
       <c r="B135" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>135656967</v>
       </c>
       <c r="B136" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>135656968</v>
       </c>
       <c r="B137" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>135656969</v>
       </c>
       <c r="B138" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>135656970</v>
       </c>
       <c r="B139" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>135656971</v>
       </c>
       <c r="B140" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>135656972</v>
       </c>
       <c r="B141" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>135656973</v>
       </c>
       <c r="B142" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135656974</v>
       </c>
       <c r="B143" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>135656975</v>
       </c>
       <c r="B144" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>135656976</v>
       </c>
       <c r="B145" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>135656977</v>
       </c>
       <c r="B146" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>135656978</v>
       </c>
       <c r="B147" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>135656979</v>
       </c>
       <c r="B148" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>135656981</v>
       </c>
       <c r="B149" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>135656982</v>
       </c>
       <c r="B150" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>135656987</v>
       </c>
       <c r="B151" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>135656989</v>
       </c>
       <c r="B152" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>135656992</v>
       </c>
       <c r="B153" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>135656993</v>
       </c>
       <c r="B154" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>135656997</v>
       </c>
       <c r="B155" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>135656998</v>
       </c>
       <c r="B156" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>135656999</v>
       </c>
       <c r="B157" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>135657001</v>
       </c>
       <c r="B158" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>135657002</v>
       </c>
       <c r="B159" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>135657003</v>
       </c>
       <c r="B160" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>135657004</v>
       </c>
       <c r="B161" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>135657005</v>
       </c>
       <c r="B162" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>135657006</v>
       </c>
       <c r="B163" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>135657007</v>
       </c>
       <c r="B164" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>135657008</v>
       </c>
       <c r="B165" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>135657010</v>
       </c>
       <c r="B166" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>135657011</v>
       </c>
       <c r="B167" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>135657016</v>
       </c>
       <c r="B168" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>135657017</v>
       </c>
       <c r="B169" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>135657018</v>
       </c>
       <c r="B170" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>135657019</v>
       </c>
       <c r="B171" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>135657020</v>
       </c>
       <c r="B172" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>135657023</v>
       </c>
       <c r="B173" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>135657024</v>
       </c>
       <c r="B174" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>135657025</v>
       </c>
       <c r="B175" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>135657029</v>
       </c>
       <c r="B176" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>135657030</v>
       </c>
       <c r="B177" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>135657032</v>
       </c>
       <c r="B178" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>135657033</v>
       </c>
       <c r="B179" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>135657034</v>
       </c>
       <c r="B180" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>135657039</v>
       </c>
       <c r="B181" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>135657040</v>
       </c>
       <c r="B182" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>135657041</v>
       </c>
       <c r="B183" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>135657042</v>
       </c>
       <c r="B184" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>135657044</v>
       </c>
       <c r="B185" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>135657045</v>
       </c>
       <c r="B186" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135601119</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135657014</v>
       </c>
       <c r="B4" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135600489</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135657035</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135657036</v>
       </c>
       <c r="B7" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135657038</v>
       </c>
       <c r="B8" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>135600514</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135657013</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>135657015</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>135657000</v>
       </c>
       <c r="B30" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>135656980</v>
       </c>
       <c r="B31" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>135657022</v>
       </c>
       <c r="B32" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>135657043</v>
       </c>
       <c r="B39" t="n">
-        <v>99328</v>
+        <v>99329</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>135597460</v>
       </c>
       <c r="B81" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>135597656</v>
       </c>
       <c r="B82" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>135597873</v>
       </c>
       <c r="B83" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135597960</v>
       </c>
       <c r="B84" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>135598014</v>
       </c>
       <c r="B85" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>135598068</v>
       </c>
       <c r="B86" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>135598373</v>
       </c>
       <c r="B87" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>135598420</v>
       </c>
       <c r="B88" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>135598509</v>
       </c>
       <c r="B89" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>135598562</v>
       </c>
       <c r="B90" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>135598590</v>
       </c>
       <c r="B91" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>135598647</v>
       </c>
       <c r="B92" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>135598703</v>
       </c>
       <c r="B93" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>135598769</v>
       </c>
       <c r="B94" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>135598854</v>
       </c>
       <c r="B95" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>135598878</v>
       </c>
       <c r="B96" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>135598959</v>
       </c>
       <c r="B97" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>135598992</v>
       </c>
       <c r="B98" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>135599030</v>
       </c>
       <c r="B99" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>135599166</v>
       </c>
       <c r="B100" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>135599188</v>
       </c>
       <c r="B101" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135599231</v>
       </c>
       <c r="B102" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>135599262</v>
       </c>
       <c r="B103" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>135599343</v>
       </c>
       <c r="B104" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>135599579</v>
       </c>
       <c r="B105" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>135599640</v>
       </c>
       <c r="B106" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>135599693</v>
       </c>
       <c r="B107" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>135600266</v>
       </c>
       <c r="B108" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>135600329</v>
       </c>
       <c r="B109" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>135600739</v>
       </c>
       <c r="B110" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>135600767</v>
       </c>
       <c r="B111" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>135600810</v>
       </c>
       <c r="B112" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>135600822</v>
       </c>
       <c r="B113" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>135600944</v>
       </c>
       <c r="B114" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>135601170</v>
       </c>
       <c r="B115" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>135601231</v>
       </c>
       <c r="B116" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>135601270</v>
       </c>
       <c r="B117" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>135601309</v>
       </c>
       <c r="B118" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>135601357</v>
       </c>
       <c r="B119" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>135601440</v>
       </c>
       <c r="B120" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>135601472</v>
       </c>
       <c r="B121" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>135601508</v>
       </c>
       <c r="B122" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>135656952</v>
       </c>
       <c r="B123" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>135656953</v>
       </c>
       <c r="B124" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>135656955</v>
       </c>
       <c r="B125" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>135656957</v>
       </c>
       <c r="B126" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>135656958</v>
       </c>
       <c r="B127" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>135656959</v>
       </c>
       <c r="B128" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>135656960</v>
       </c>
       <c r="B129" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>135656961</v>
       </c>
       <c r="B130" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>135656962</v>
       </c>
       <c r="B131" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>135656963</v>
       </c>
       <c r="B132" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>135656964</v>
       </c>
       <c r="B133" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>135656965</v>
       </c>
       <c r="B134" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>135656966</v>
       </c>
       <c r="B135" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>135656967</v>
       </c>
       <c r="B136" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>135656968</v>
       </c>
       <c r="B137" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>135656969</v>
       </c>
       <c r="B138" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>135656970</v>
       </c>
       <c r="B139" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>135656971</v>
       </c>
       <c r="B140" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>135656972</v>
       </c>
       <c r="B141" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>135656973</v>
       </c>
       <c r="B142" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135656974</v>
       </c>
       <c r="B143" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>135656975</v>
       </c>
       <c r="B144" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>135656976</v>
       </c>
       <c r="B145" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>135656977</v>
       </c>
       <c r="B146" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>135656978</v>
       </c>
       <c r="B147" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>135656979</v>
       </c>
       <c r="B148" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>135656981</v>
       </c>
       <c r="B149" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>135656982</v>
       </c>
       <c r="B150" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>135656987</v>
       </c>
       <c r="B151" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>135656989</v>
       </c>
       <c r="B152" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>135656992</v>
       </c>
       <c r="B153" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>135656993</v>
       </c>
       <c r="B154" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>135656997</v>
       </c>
       <c r="B155" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>135656998</v>
       </c>
       <c r="B156" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>135656999</v>
       </c>
       <c r="B157" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>135657001</v>
       </c>
       <c r="B158" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>135657002</v>
       </c>
       <c r="B159" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>135657003</v>
       </c>
       <c r="B160" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>135657004</v>
       </c>
       <c r="B161" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>135657005</v>
       </c>
       <c r="B162" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>135657006</v>
       </c>
       <c r="B163" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>135657007</v>
       </c>
       <c r="B164" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>135657008</v>
       </c>
       <c r="B165" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>135657010</v>
       </c>
       <c r="B166" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>135657011</v>
       </c>
       <c r="B167" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>135657016</v>
       </c>
       <c r="B168" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>135657017</v>
       </c>
       <c r="B169" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>135657018</v>
       </c>
       <c r="B170" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>135657019</v>
       </c>
       <c r="B171" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>135657020</v>
       </c>
       <c r="B172" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>135657023</v>
       </c>
       <c r="B173" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>135657024</v>
       </c>
       <c r="B174" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>135657025</v>
       </c>
       <c r="B175" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>135657029</v>
       </c>
       <c r="B176" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>135657030</v>
       </c>
       <c r="B177" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>135657032</v>
       </c>
       <c r="B178" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>135657033</v>
       </c>
       <c r="B179" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>135657034</v>
       </c>
       <c r="B180" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>135657039</v>
       </c>
       <c r="B181" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>135657040</v>
       </c>
       <c r="B182" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>135657041</v>
       </c>
       <c r="B183" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>135657042</v>
       </c>
       <c r="B184" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>135657044</v>
       </c>
       <c r="B185" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>135657045</v>
       </c>
       <c r="B186" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>135657014</v>
       </c>
       <c r="B4" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135600489</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135657035</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135657036</v>
       </c>
       <c r="B7" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135657038</v>
       </c>
       <c r="B8" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>135657043</v>
       </c>
       <c r="B39" t="n">
-        <v>99329</v>
+        <v>99330</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>135597460</v>
       </c>
       <c r="B81" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>135597656</v>
       </c>
       <c r="B82" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>135597873</v>
       </c>
       <c r="B83" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135597960</v>
       </c>
       <c r="B84" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>135598014</v>
       </c>
       <c r="B85" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>135598068</v>
       </c>
       <c r="B86" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>135598373</v>
       </c>
       <c r="B87" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>135598420</v>
       </c>
       <c r="B88" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>135598509</v>
       </c>
       <c r="B89" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>135598562</v>
       </c>
       <c r="B90" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>135598590</v>
       </c>
       <c r="B91" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>135598647</v>
       </c>
       <c r="B92" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>135598703</v>
       </c>
       <c r="B93" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>135598769</v>
       </c>
       <c r="B94" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>135598854</v>
       </c>
       <c r="B95" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>135598878</v>
       </c>
       <c r="B96" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>135598959</v>
       </c>
       <c r="B97" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>135598992</v>
       </c>
       <c r="B98" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>135599030</v>
       </c>
       <c r="B99" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>135599166</v>
       </c>
       <c r="B100" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>135599188</v>
       </c>
       <c r="B101" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>135599231</v>
       </c>
       <c r="B102" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>135599262</v>
       </c>
       <c r="B103" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>135599343</v>
       </c>
       <c r="B104" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>135599579</v>
       </c>
       <c r="B105" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>135599640</v>
       </c>
       <c r="B106" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>135599693</v>
       </c>
       <c r="B107" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>135600266</v>
       </c>
       <c r="B108" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>135600329</v>
       </c>
       <c r="B109" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>135600739</v>
       </c>
       <c r="B110" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>135600767</v>
       </c>
       <c r="B111" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>135600810</v>
       </c>
       <c r="B112" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>135600822</v>
       </c>
       <c r="B113" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>135600944</v>
       </c>
       <c r="B114" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>135601170</v>
       </c>
       <c r="B115" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>135601231</v>
       </c>
       <c r="B116" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>135601270</v>
       </c>
       <c r="B117" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>135601309</v>
       </c>
       <c r="B118" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>135601357</v>
       </c>
       <c r="B119" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>135601440</v>
       </c>
       <c r="B120" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>135601472</v>
       </c>
       <c r="B121" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>135601508</v>
       </c>
       <c r="B122" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>135656952</v>
       </c>
       <c r="B123" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>135656953</v>
       </c>
       <c r="B124" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>135656955</v>
       </c>
       <c r="B125" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>135656957</v>
       </c>
       <c r="B126" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>135656958</v>
       </c>
       <c r="B127" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>135656959</v>
       </c>
       <c r="B128" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>135656960</v>
       </c>
       <c r="B129" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>135656961</v>
       </c>
       <c r="B130" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>135656962</v>
       </c>
       <c r="B131" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>135656963</v>
       </c>
       <c r="B132" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>135656964</v>
       </c>
       <c r="B133" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>135656965</v>
       </c>
       <c r="B134" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>135656966</v>
       </c>
       <c r="B135" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>135656967</v>
       </c>
       <c r="B136" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>135656968</v>
       </c>
       <c r="B137" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>135656969</v>
       </c>
       <c r="B138" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>135656970</v>
       </c>
       <c r="B139" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>135656971</v>
       </c>
       <c r="B140" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>135656972</v>
       </c>
       <c r="B141" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>135656973</v>
       </c>
       <c r="B142" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135656974</v>
       </c>
       <c r="B143" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>135656975</v>
       </c>
       <c r="B144" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>135656976</v>
       </c>
       <c r="B145" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>135656977</v>
       </c>
       <c r="B146" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>135656978</v>
       </c>
       <c r="B147" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>135656979</v>
       </c>
       <c r="B148" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>135656981</v>
       </c>
       <c r="B149" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>135656982</v>
       </c>
       <c r="B150" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>135656987</v>
       </c>
       <c r="B151" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>135656989</v>
       </c>
       <c r="B152" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>135656992</v>
       </c>
       <c r="B153" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>135656993</v>
       </c>
       <c r="B154" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>135656997</v>
       </c>
       <c r="B155" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>135656998</v>
       </c>
       <c r="B156" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>135656999</v>
       </c>
       <c r="B157" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>135657001</v>
       </c>
       <c r="B158" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>135657002</v>
       </c>
       <c r="B159" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>135657003</v>
       </c>
       <c r="B160" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>135657004</v>
       </c>
       <c r="B161" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>135657005</v>
       </c>
       <c r="B162" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>135657006</v>
       </c>
       <c r="B163" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>135657007</v>
       </c>
       <c r="B164" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>135657008</v>
       </c>
       <c r="B165" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>135657010</v>
       </c>
       <c r="B166" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>135657011</v>
       </c>
       <c r="B167" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>135657016</v>
       </c>
       <c r="B168" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>135657017</v>
       </c>
       <c r="B169" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>135657018</v>
       </c>
       <c r="B170" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>135657019</v>
       </c>
       <c r="B171" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>135657020</v>
       </c>
       <c r="B172" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>135657023</v>
       </c>
       <c r="B173" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>135657024</v>
       </c>
       <c r="B174" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>135657025</v>
       </c>
       <c r="B175" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>135657029</v>
       </c>
       <c r="B176" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>135657030</v>
       </c>
       <c r="B177" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>135657032</v>
       </c>
       <c r="B178" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>135657033</v>
       </c>
       <c r="B179" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>135657034</v>
       </c>
       <c r="B180" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>135657039</v>
       </c>
       <c r="B181" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>135657040</v>
       </c>
       <c r="B182" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>135657041</v>
       </c>
       <c r="B183" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>135657042</v>
       </c>
       <c r="B184" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>135657044</v>
       </c>
       <c r="B185" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>135657045</v>
       </c>
       <c r="B186" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>135657014</v>
       </c>
       <c r="B4" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135657035</v>
       </c>
       <c r="B6" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135657036</v>
       </c>
       <c r="B7" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135657038</v>
       </c>
       <c r="B8" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135657013</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>135657015</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>135657000</v>
       </c>
       <c r="B30" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>135656980</v>
       </c>
       <c r="B31" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>135657022</v>
       </c>
       <c r="B32" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>135657043</v>
       </c>
       <c r="B39" t="n">
-        <v>99330</v>
+        <v>99331</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>135656952</v>
       </c>
       <c r="B123" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>135656953</v>
       </c>
       <c r="B124" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>135656955</v>
       </c>
       <c r="B125" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>135656957</v>
       </c>
       <c r="B126" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>135656958</v>
       </c>
       <c r="B127" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>135656959</v>
       </c>
       <c r="B128" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>135656960</v>
       </c>
       <c r="B129" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>135656961</v>
       </c>
       <c r="B130" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>135656962</v>
       </c>
       <c r="B131" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>135656963</v>
       </c>
       <c r="B132" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>135656964</v>
       </c>
       <c r="B133" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>135656965</v>
       </c>
       <c r="B134" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>135656966</v>
       </c>
       <c r="B135" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>135656967</v>
       </c>
       <c r="B136" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>135656968</v>
       </c>
       <c r="B137" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>135656969</v>
       </c>
       <c r="B138" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>135656970</v>
       </c>
       <c r="B139" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>135656971</v>
       </c>
       <c r="B140" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>135656972</v>
       </c>
       <c r="B141" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>135656973</v>
       </c>
       <c r="B142" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135656974</v>
       </c>
       <c r="B143" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>135656975</v>
       </c>
       <c r="B144" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>135656976</v>
       </c>
       <c r="B145" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>135656977</v>
       </c>
       <c r="B146" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>135656978</v>
       </c>
       <c r="B147" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>135656979</v>
       </c>
       <c r="B148" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>135656981</v>
       </c>
       <c r="B149" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>135656982</v>
       </c>
       <c r="B150" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>135656987</v>
       </c>
       <c r="B151" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>135656989</v>
       </c>
       <c r="B152" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>135656992</v>
       </c>
       <c r="B153" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>135656993</v>
       </c>
       <c r="B154" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>135656997</v>
       </c>
       <c r="B155" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>135656998</v>
       </c>
       <c r="B156" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>135656999</v>
       </c>
       <c r="B157" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>135657001</v>
       </c>
       <c r="B158" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>135657002</v>
       </c>
       <c r="B159" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>135657003</v>
       </c>
       <c r="B160" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>135657004</v>
       </c>
       <c r="B161" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>135657005</v>
       </c>
       <c r="B162" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>135657006</v>
       </c>
       <c r="B163" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>135657007</v>
       </c>
       <c r="B164" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>135657008</v>
       </c>
       <c r="B165" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>135657010</v>
       </c>
       <c r="B166" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>135657011</v>
       </c>
       <c r="B167" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>135657016</v>
       </c>
       <c r="B168" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>135657017</v>
       </c>
       <c r="B169" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>135657018</v>
       </c>
       <c r="B170" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>135657019</v>
       </c>
       <c r="B171" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>135657020</v>
       </c>
       <c r="B172" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>135657023</v>
       </c>
       <c r="B173" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>135657024</v>
       </c>
       <c r="B174" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>135657025</v>
       </c>
       <c r="B175" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>135657029</v>
       </c>
       <c r="B176" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>135657030</v>
       </c>
       <c r="B177" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>135657032</v>
       </c>
       <c r="B178" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>135657033</v>
       </c>
       <c r="B179" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>135657034</v>
       </c>
       <c r="B180" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>135657039</v>
       </c>
       <c r="B181" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>135657040</v>
       </c>
       <c r="B182" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>135657041</v>
       </c>
       <c r="B183" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>135657042</v>
       </c>
       <c r="B184" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>135657044</v>
       </c>
       <c r="B185" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>135657045</v>
       </c>
       <c r="B186" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>135657014</v>
       </c>
       <c r="B4" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135657035</v>
       </c>
       <c r="B6" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135657036</v>
       </c>
       <c r="B7" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135657038</v>
       </c>
       <c r="B8" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135657013</v>
       </c>
       <c r="B17" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>135657015</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>135657000</v>
       </c>
       <c r="B30" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>135656980</v>
       </c>
       <c r="B31" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>135657022</v>
       </c>
       <c r="B32" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>135657043</v>
       </c>
       <c r="B39" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>135656952</v>
       </c>
       <c r="B123" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>135656953</v>
       </c>
       <c r="B124" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>135656955</v>
       </c>
       <c r="B125" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>135656957</v>
       </c>
       <c r="B126" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>135656958</v>
       </c>
       <c r="B127" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>135656959</v>
       </c>
       <c r="B128" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>135656960</v>
       </c>
       <c r="B129" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>135656961</v>
       </c>
       <c r="B130" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>135656962</v>
       </c>
       <c r="B131" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>135656963</v>
       </c>
       <c r="B132" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>135656964</v>
       </c>
       <c r="B133" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>135656965</v>
       </c>
       <c r="B134" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>135656966</v>
       </c>
       <c r="B135" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>135656967</v>
       </c>
       <c r="B136" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>135656968</v>
       </c>
       <c r="B137" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>135656969</v>
       </c>
       <c r="B138" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>135656970</v>
       </c>
       <c r="B139" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>135656971</v>
       </c>
       <c r="B140" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>135656972</v>
       </c>
       <c r="B141" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>135656973</v>
       </c>
       <c r="B142" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135656974</v>
       </c>
       <c r="B143" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>135656975</v>
       </c>
       <c r="B144" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>135656976</v>
       </c>
       <c r="B145" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>135656977</v>
       </c>
       <c r="B146" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>135656978</v>
       </c>
       <c r="B147" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>135656979</v>
       </c>
       <c r="B148" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>135656981</v>
       </c>
       <c r="B149" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>135656982</v>
       </c>
       <c r="B150" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>135656987</v>
       </c>
       <c r="B151" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>135656989</v>
       </c>
       <c r="B152" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>135656992</v>
       </c>
       <c r="B153" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>135656993</v>
       </c>
       <c r="B154" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>135656997</v>
       </c>
       <c r="B155" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>135656998</v>
       </c>
       <c r="B156" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>135656999</v>
       </c>
       <c r="B157" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>135657001</v>
       </c>
       <c r="B158" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>135657002</v>
       </c>
       <c r="B159" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>135657003</v>
       </c>
       <c r="B160" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>135657004</v>
       </c>
       <c r="B161" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>135657005</v>
       </c>
       <c r="B162" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>135657006</v>
       </c>
       <c r="B163" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>135657007</v>
       </c>
       <c r="B164" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>135657008</v>
       </c>
       <c r="B165" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>135657010</v>
       </c>
       <c r="B166" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>135657011</v>
       </c>
       <c r="B167" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>135657016</v>
       </c>
       <c r="B168" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>135657017</v>
       </c>
       <c r="B169" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>135657018</v>
       </c>
       <c r="B170" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>135657019</v>
       </c>
       <c r="B171" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>135657020</v>
       </c>
       <c r="B172" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>135657023</v>
       </c>
       <c r="B173" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>135657024</v>
       </c>
       <c r="B174" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>135657025</v>
       </c>
       <c r="B175" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>135657029</v>
       </c>
       <c r="B176" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>135657030</v>
       </c>
       <c r="B177" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>135657032</v>
       </c>
       <c r="B178" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>135657033</v>
       </c>
       <c r="B179" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>135657034</v>
       </c>
       <c r="B180" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>135657039</v>
       </c>
       <c r="B181" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>135657040</v>
       </c>
       <c r="B182" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>135657041</v>
       </c>
       <c r="B183" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>135657042</v>
       </c>
       <c r="B184" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>135657044</v>
       </c>
       <c r="B185" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>135657045</v>
       </c>
       <c r="B186" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 46633-2023 artfynd.xlsx
+++ b/artfynd/A 46633-2023 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>135657014</v>
       </c>
       <c r="B4" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135657035</v>
       </c>
       <c r="B6" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135657036</v>
       </c>
       <c r="B7" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135657038</v>
       </c>
       <c r="B8" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135657013</v>
       </c>
       <c r="B17" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>135657015</v>
       </c>
       <c r="B18" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>135657000</v>
       </c>
       <c r="B30" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>135656980</v>
       </c>
       <c r="B31" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>135657022</v>
       </c>
       <c r="B32" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>135657043</v>
       </c>
       <c r="B39" t="n">
-        <v>99337</v>
+        <v>99338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>135656952</v>
       </c>
       <c r="B123" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>135656953</v>
       </c>
       <c r="B124" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>135656955</v>
       </c>
       <c r="B125" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>135656957</v>
       </c>
       <c r="B126" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>135656958</v>
       </c>
       <c r="B127" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>135656959</v>
       </c>
       <c r="B128" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>135656960</v>
       </c>
       <c r="B129" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>135656961</v>
       </c>
       <c r="B130" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>135656962</v>
       </c>
       <c r="B131" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>135656963</v>
       </c>
       <c r="B132" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>135656964</v>
       </c>
       <c r="B133" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>135656965</v>
       </c>
       <c r="B134" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>135656966</v>
       </c>
       <c r="B135" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>135656967</v>
       </c>
       <c r="B136" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>135656968</v>
       </c>
       <c r="B137" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>135656969</v>
       </c>
       <c r="B138" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>135656970</v>
       </c>
       <c r="B139" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>135656971</v>
       </c>
       <c r="B140" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>135656972</v>
       </c>
       <c r="B141" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>135656973</v>
       </c>
       <c r="B142" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135656974</v>
       </c>
       <c r="B143" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>135656975</v>
       </c>
       <c r="B144" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>135656976</v>
       </c>
       <c r="B145" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>135656977</v>
       </c>
       <c r="B146" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>135656978</v>
       </c>
       <c r="B147" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>135656979</v>
       </c>
       <c r="B148" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>135656981</v>
       </c>
       <c r="B149" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>135656982</v>
       </c>
       <c r="B150" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>135656987</v>
       </c>
       <c r="B151" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>135656989</v>
       </c>
       <c r="B152" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>135656992</v>
       </c>
       <c r="B153" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>135656993</v>
       </c>
       <c r="B154" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>135656997</v>
       </c>
       <c r="B155" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>135656998</v>
       </c>
       <c r="B156" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>135656999</v>
       </c>
       <c r="B157" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>135657001</v>
       </c>
       <c r="B158" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>135657002</v>
       </c>
       <c r="B159" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>135657003</v>
       </c>
       <c r="B160" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>135657004</v>
       </c>
       <c r="B161" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>135657005</v>
       </c>
       <c r="B162" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>135657006</v>
       </c>
       <c r="B163" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>135657007</v>
       </c>
       <c r="B164" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>135657008</v>
       </c>
       <c r="B165" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>135657010</v>
       </c>
       <c r="B166" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>135657011</v>
       </c>
       <c r="B167" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>135657016</v>
       </c>
       <c r="B168" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>135657017</v>
       </c>
       <c r="B169" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>135657018</v>
       </c>
       <c r="B170" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>135657019</v>
       </c>
       <c r="B171" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>135657020</v>
       </c>
       <c r="B172" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>135657023</v>
       </c>
       <c r="B173" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>135657024</v>
       </c>
       <c r="B174" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>135657025</v>
       </c>
       <c r="B175" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>135657029</v>
       </c>
       <c r="B176" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>135657030</v>
       </c>
       <c r="B177" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>135657032</v>
       </c>
       <c r="B178" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>135657033</v>
       </c>
       <c r="B179" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>135657034</v>
       </c>
       <c r="B180" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>135657039</v>
       </c>
       <c r="B181" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>135657040</v>
       </c>
       <c r="B182" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>135657041</v>
       </c>
       <c r="B183" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>135657042</v>
       </c>
       <c r="B184" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>135657044</v>
       </c>
       <c r="B185" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>135657045</v>
       </c>
       <c r="B186" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
